--- a/anexos/Processo Nº 12941255 - JOELSON SOUSA JUNIOR/PEÇAS TÉCNICAS/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/anexos/Processo Nº 12941255 - JOELSON SOUSA JUNIOR/PEÇAS TÉCNICAS/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\1. AVALIAÇÕES\01. AVALIAÇÕES SICREDI\01. RURAL\07. JULHO\Processo Nº 12941255 - JOELSON SOUSA JUNIOR\PEÇAS TÉCNICAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dista\Desktop\projeto_laudo\anexos\Processo Nº 12941255 - JOELSON SOUSA JUNIOR\PEÇAS TÉCNICAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504AB4C1-F345-4040-A6D9-ABC5BE91B4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6930" tabRatio="874" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="874" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
     <sheet name="FATORES" sheetId="2" r:id="rId2"/>
     <sheet name="UTIL_LAUDO" sheetId="13" r:id="rId3"/>
-    <sheet name="AREA UTIL " sheetId="3" r:id="rId4"/>
+    <sheet name="AREA UTIL" sheetId="3" r:id="rId4"/>
     <sheet name="AMOSTRAS" sheetId="4" r:id="rId5"/>
     <sheet name="QUADRO" sheetId="5" r:id="rId6"/>
     <sheet name="PLANILHA HOMOG" sheetId="6" r:id="rId7"/>
@@ -30,30 +31,17 @@
     <definedName name="Print_Area" localSheetId="10">'LAUDO DE AVALIAÇÃO 12-12.4'!$B$1:$H$24</definedName>
     <definedName name="Print_Area" localSheetId="11">'LAUDO DE AVALIAÇÃO 13'!$B$1:$G$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>valec</author>
   </authors>
   <commentList>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
       <text>
         <r>
           <rPr>
@@ -71,12 +59,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>valec</author>
   </authors>
   <commentList>
-    <comment ref="D5" authorId="0" shapeId="0">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1089,7 +1077,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="12">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -2910,95 +2898,95 @@
     <xf numFmtId="0" fontId="63" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3019,56 +3007,38 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3081,52 +3051,82 @@
     <xf numFmtId="0" fontId="57" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="24" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3136,157 +3136,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3296,29 +3200,122 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3328,162 +3325,163 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="170" fontId="47" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="172" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="43" fontId="39" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3491,26 +3489,16 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3526,25 +3514,25 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3673,9 +3661,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3713,9 +3701,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3750,7 +3738,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3785,7 +3773,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3958,12 +3946,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:M47"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="3" spans="2:13">
-      <c r="B3" s="249" t="s">
+      <c r="B3" s="247" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="256"/>
@@ -3976,21 +3964,21 @@
       <c r="J3" s="256"/>
       <c r="K3" s="256"/>
       <c r="L3" s="256"/>
-      <c r="M3" s="261"/>
+      <c r="M3" s="257"/>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="262"/>
-      <c r="C4" s="259"/>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
-      <c r="M4" s="263"/>
+      <c r="B4" s="269"/>
+      <c r="C4" s="251"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="M4" s="259"/>
     </row>
     <row r="5" spans="2:13" ht="19.5" customHeight="1">
       <c r="B5" s="122"/>
@@ -4021,100 +4009,100 @@
       <c r="M6" s="107"/>
     </row>
     <row r="7" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B7" s="247" t="s">
+      <c r="B7" s="252" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="248"/>
-      <c r="D7" s="248"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="248"/>
-      <c r="H7" s="248"/>
-      <c r="I7" s="248"/>
-      <c r="J7" s="248"/>
-      <c r="K7" s="248"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="253"/>
+      <c r="C7" s="253"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="270"/>
+      <c r="F7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="253"/>
+      <c r="I7" s="253"/>
+      <c r="J7" s="253"/>
+      <c r="K7" s="253"/>
+      <c r="L7" s="253"/>
+      <c r="M7" s="263"/>
     </row>
     <row r="8" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B8" s="247" t="s">
+      <c r="B8" s="252" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="248"/>
-      <c r="D8" s="248"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="248"/>
-      <c r="G8" s="248"/>
-      <c r="H8" s="248"/>
-      <c r="I8" s="248"/>
-      <c r="J8" s="248"/>
-      <c r="K8" s="248"/>
-      <c r="L8" s="248"/>
-      <c r="M8" s="253"/>
+      <c r="C8" s="253"/>
+      <c r="D8" s="253"/>
+      <c r="E8" s="270"/>
+      <c r="F8" s="253"/>
+      <c r="G8" s="253"/>
+      <c r="H8" s="253"/>
+      <c r="I8" s="253"/>
+      <c r="J8" s="253"/>
+      <c r="K8" s="253"/>
+      <c r="L8" s="253"/>
+      <c r="M8" s="263"/>
     </row>
     <row r="9" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B9" s="247" t="s">
+      <c r="B9" s="252" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="248"/>
-      <c r="D9" s="248"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
-      <c r="M9" s="253"/>
+      <c r="C9" s="253"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="270"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="253"/>
+      <c r="M9" s="263"/>
     </row>
     <row r="10" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B10" s="247" t="s">
+      <c r="B10" s="252" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="248"/>
-      <c r="D10" s="248"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="248"/>
-      <c r="G10" s="248"/>
-      <c r="H10" s="248"/>
-      <c r="I10" s="248"/>
-      <c r="J10" s="248"/>
-      <c r="K10" s="248"/>
-      <c r="L10" s="248"/>
-      <c r="M10" s="253"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="270"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="253"/>
+      <c r="I10" s="253"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="253"/>
+      <c r="L10" s="253"/>
+      <c r="M10" s="263"/>
     </row>
     <row r="11" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B11" s="247" t="s">
+      <c r="B11" s="252" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="248"/>
-      <c r="D11" s="248"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
-      <c r="M11" s="253"/>
+      <c r="C11" s="253"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="270"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="253"/>
+      <c r="H11" s="253"/>
+      <c r="I11" s="253"/>
+      <c r="J11" s="253"/>
+      <c r="K11" s="253"/>
+      <c r="L11" s="253"/>
+      <c r="M11" s="263"/>
     </row>
     <row r="12" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B12" s="247" t="s">
+      <c r="B12" s="252" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="248"/>
-      <c r="D12" s="248"/>
-      <c r="E12" s="252"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="248"/>
-      <c r="L12" s="248"/>
-      <c r="M12" s="253"/>
+      <c r="C12" s="253"/>
+      <c r="D12" s="253"/>
+      <c r="E12" s="270"/>
+      <c r="F12" s="253"/>
+      <c r="G12" s="253"/>
+      <c r="H12" s="253"/>
+      <c r="I12" s="253"/>
+      <c r="J12" s="253"/>
+      <c r="K12" s="253"/>
+      <c r="L12" s="253"/>
+      <c r="M12" s="263"/>
     </row>
     <row r="13" spans="2:13" ht="17.25" customHeight="1">
       <c r="B13" s="108"/>
@@ -4173,20 +4161,20 @@
       <c r="M16" s="122"/>
     </row>
     <row r="17" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B17" s="254" t="s">
+      <c r="B17" s="281" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="248"/>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
-      <c r="M17" s="248"/>
+      <c r="C17" s="253"/>
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="253"/>
+      <c r="I17" s="253"/>
+      <c r="J17" s="253"/>
+      <c r="K17" s="253"/>
+      <c r="L17" s="253"/>
+      <c r="M17" s="253"/>
     </row>
     <row r="18" spans="2:13" ht="19.5" customHeight="1">
       <c r="B18" s="111"/>
@@ -4203,12 +4191,12 @@
       <c r="M18" s="111"/>
     </row>
     <row r="19" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="282" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="256"/>
       <c r="D19" s="256"/>
-      <c r="E19" s="260"/>
+      <c r="E19" s="280"/>
       <c r="F19" s="256"/>
       <c r="G19" s="256"/>
       <c r="H19" s="256"/>
@@ -4216,137 +4204,137 @@
       <c r="J19" s="256"/>
       <c r="K19" s="256"/>
       <c r="L19" s="256"/>
-      <c r="M19" s="261"/>
+      <c r="M19" s="257"/>
     </row>
     <row r="20" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="252" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="248"/>
-      <c r="D20" s="248"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="248"/>
-      <c r="G20" s="248"/>
-      <c r="H20" s="248"/>
-      <c r="I20" s="248"/>
-      <c r="J20" s="248"/>
-      <c r="K20" s="248"/>
-      <c r="L20" s="248"/>
-      <c r="M20" s="253"/>
+      <c r="C20" s="253"/>
+      <c r="D20" s="253"/>
+      <c r="E20" s="270"/>
+      <c r="F20" s="253"/>
+      <c r="G20" s="253"/>
+      <c r="H20" s="253"/>
+      <c r="I20" s="253"/>
+      <c r="J20" s="253"/>
+      <c r="K20" s="253"/>
+      <c r="L20" s="253"/>
+      <c r="M20" s="263"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B21" s="247" t="s">
+      <c r="B21" s="252" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="248"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="252"/>
-      <c r="F21" s="248"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
-      <c r="I21" s="248"/>
-      <c r="J21" s="248"/>
-      <c r="K21" s="248"/>
-      <c r="L21" s="248"/>
-      <c r="M21" s="253"/>
+      <c r="C21" s="253"/>
+      <c r="D21" s="253"/>
+      <c r="E21" s="270"/>
+      <c r="F21" s="253"/>
+      <c r="G21" s="253"/>
+      <c r="H21" s="253"/>
+      <c r="I21" s="253"/>
+      <c r="J21" s="253"/>
+      <c r="K21" s="253"/>
+      <c r="L21" s="253"/>
+      <c r="M21" s="263"/>
     </row>
     <row r="22" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B22" s="270" t="s">
+      <c r="B22" s="277" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="259"/>
-      <c r="D22" s="259"/>
-      <c r="E22" s="264"/>
-      <c r="F22" s="259"/>
-      <c r="G22" s="259"/>
-      <c r="H22" s="259"/>
-      <c r="I22" s="259"/>
-      <c r="J22" s="259"/>
+      <c r="C22" s="251"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="271"/>
+      <c r="F22" s="251"/>
+      <c r="G22" s="251"/>
+      <c r="H22" s="251"/>
+      <c r="I22" s="251"/>
+      <c r="J22" s="251"/>
       <c r="K22" s="112"/>
-      <c r="L22" s="268"/>
-      <c r="M22" s="263"/>
+      <c r="L22" s="275"/>
+      <c r="M22" s="259"/>
     </row>
     <row r="23" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B23" s="249" t="s">
+      <c r="B23" s="247" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="250"/>
-      <c r="D23" s="250"/>
-      <c r="E23" s="250"/>
-      <c r="F23" s="250"/>
-      <c r="G23" s="250"/>
-      <c r="H23" s="250"/>
-      <c r="I23" s="250"/>
-      <c r="J23" s="250"/>
-      <c r="K23" s="250"/>
-      <c r="L23" s="250"/>
-      <c r="M23" s="251"/>
+      <c r="C23" s="248"/>
+      <c r="D23" s="248"/>
+      <c r="E23" s="248"/>
+      <c r="F23" s="248"/>
+      <c r="G23" s="248"/>
+      <c r="H23" s="248"/>
+      <c r="I23" s="248"/>
+      <c r="J23" s="248"/>
+      <c r="K23" s="248"/>
+      <c r="L23" s="248"/>
+      <c r="M23" s="249"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="257" t="s">
+      <c r="B24" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="250"/>
-      <c r="D24" s="251"/>
-      <c r="E24" s="257" t="s">
+      <c r="C24" s="248"/>
+      <c r="D24" s="249"/>
+      <c r="E24" s="260" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="250"/>
-      <c r="G24" s="251"/>
-      <c r="H24" s="257" t="s">
+      <c r="F24" s="248"/>
+      <c r="G24" s="249"/>
+      <c r="H24" s="260" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="250"/>
-      <c r="J24" s="251"/>
-      <c r="K24" s="257" t="s">
+      <c r="I24" s="248"/>
+      <c r="J24" s="249"/>
+      <c r="K24" s="260" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="250"/>
-      <c r="M24" s="251"/>
+      <c r="L24" s="248"/>
+      <c r="M24" s="249"/>
     </row>
     <row r="25" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B25" s="267"/>
+      <c r="B25" s="274"/>
       <c r="C25" s="256"/>
-      <c r="D25" s="261"/>
-      <c r="E25" s="276"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="274"/>
+      <c r="D25" s="257"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="253"/>
+      <c r="G25" s="253"/>
+      <c r="H25" s="255"/>
       <c r="I25" s="256"/>
-      <c r="J25" s="261"/>
-      <c r="K25" s="269"/>
+      <c r="J25" s="257"/>
+      <c r="K25" s="276"/>
       <c r="L25" s="256"/>
-      <c r="M25" s="261"/>
+      <c r="M25" s="257"/>
     </row>
     <row r="26" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B26" s="265"/>
-      <c r="C26" s="259"/>
-      <c r="D26" s="263"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="259"/>
-      <c r="G26" s="259"/>
-      <c r="H26" s="266"/>
-      <c r="I26" s="259"/>
-      <c r="J26" s="263"/>
-      <c r="K26" s="271"/>
-      <c r="L26" s="259"/>
-      <c r="M26" s="263"/>
+      <c r="B26" s="272"/>
+      <c r="C26" s="251"/>
+      <c r="D26" s="259"/>
+      <c r="E26" s="279"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="273"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="259"/>
+      <c r="K26" s="278"/>
+      <c r="L26" s="251"/>
+      <c r="M26" s="259"/>
     </row>
     <row r="27" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B27" s="249" t="s">
+      <c r="B27" s="247" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="250"/>
-      <c r="D27" s="250"/>
-      <c r="E27" s="250"/>
-      <c r="F27" s="250"/>
-      <c r="G27" s="250"/>
-      <c r="H27" s="250"/>
-      <c r="I27" s="250"/>
-      <c r="J27" s="250"/>
-      <c r="K27" s="250"/>
-      <c r="L27" s="250"/>
-      <c r="M27" s="251"/>
+      <c r="C27" s="248"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="248"/>
+      <c r="I27" s="248"/>
+      <c r="J27" s="248"/>
+      <c r="K27" s="248"/>
+      <c r="L27" s="248"/>
+      <c r="M27" s="249"/>
     </row>
     <row r="28" spans="2:13" ht="17.25" customHeight="1">
       <c r="B28" s="113"/>
@@ -4433,100 +4421,100 @@
       <c r="M33" s="121"/>
     </row>
     <row r="34" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B34" s="249" t="s">
+      <c r="B34" s="247" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="250"/>
-      <c r="D34" s="250"/>
-      <c r="E34" s="250"/>
-      <c r="F34" s="250"/>
-      <c r="G34" s="250"/>
-      <c r="H34" s="250"/>
-      <c r="I34" s="250"/>
-      <c r="J34" s="250"/>
-      <c r="K34" s="250"/>
-      <c r="L34" s="250"/>
-      <c r="M34" s="251"/>
+      <c r="C34" s="248"/>
+      <c r="D34" s="248"/>
+      <c r="E34" s="248"/>
+      <c r="F34" s="248"/>
+      <c r="G34" s="248"/>
+      <c r="H34" s="248"/>
+      <c r="I34" s="248"/>
+      <c r="J34" s="248"/>
+      <c r="K34" s="248"/>
+      <c r="L34" s="248"/>
+      <c r="M34" s="249"/>
     </row>
     <row r="35" spans="2:13" ht="15" customHeight="1">
-      <c r="B35" s="257" t="s">
+      <c r="B35" s="260" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="250"/>
-      <c r="D35" s="250"/>
-      <c r="E35" s="251"/>
-      <c r="F35" s="257" t="s">
+      <c r="C35" s="248"/>
+      <c r="D35" s="248"/>
+      <c r="E35" s="249"/>
+      <c r="F35" s="260" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="250"/>
-      <c r="H35" s="250"/>
-      <c r="I35" s="251"/>
-      <c r="J35" s="257" t="s">
+      <c r="G35" s="248"/>
+      <c r="H35" s="248"/>
+      <c r="I35" s="249"/>
+      <c r="J35" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="250"/>
-      <c r="L35" s="250"/>
-      <c r="M35" s="251"/>
+      <c r="K35" s="248"/>
+      <c r="L35" s="248"/>
+      <c r="M35" s="249"/>
     </row>
     <row r="36" spans="2:13" ht="15" customHeight="1">
-      <c r="B36" s="280"/>
+      <c r="B36" s="266"/>
       <c r="C36" s="256"/>
       <c r="D36" s="256"/>
       <c r="E36" s="256"/>
-      <c r="F36" s="281"/>
+      <c r="F36" s="267"/>
       <c r="G36" s="256"/>
       <c r="H36" s="256"/>
       <c r="I36" s="256"/>
-      <c r="J36" s="282"/>
+      <c r="J36" s="268"/>
       <c r="K36" s="256"/>
       <c r="L36" s="256"/>
-      <c r="M36" s="261"/>
+      <c r="M36" s="257"/>
     </row>
     <row r="37" spans="2:13" ht="15" customHeight="1">
-      <c r="B37" s="273"/>
-      <c r="C37" s="248"/>
-      <c r="D37" s="248"/>
-      <c r="E37" s="248"/>
-      <c r="F37" s="279"/>
-      <c r="G37" s="248"/>
-      <c r="H37" s="248"/>
-      <c r="I37" s="248"/>
-      <c r="J37" s="277"/>
-      <c r="K37" s="248"/>
-      <c r="L37" s="248"/>
-      <c r="M37" s="253"/>
+      <c r="B37" s="254"/>
+      <c r="C37" s="253"/>
+      <c r="D37" s="253"/>
+      <c r="E37" s="253"/>
+      <c r="F37" s="265"/>
+      <c r="G37" s="253"/>
+      <c r="H37" s="253"/>
+      <c r="I37" s="253"/>
+      <c r="J37" s="262"/>
+      <c r="K37" s="253"/>
+      <c r="L37" s="253"/>
+      <c r="M37" s="263"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1">
-      <c r="B38" s="278" t="s">
+      <c r="B38" s="264" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="259"/>
-      <c r="D38" s="259"/>
-      <c r="E38" s="259"/>
-      <c r="F38" s="272"/>
-      <c r="G38" s="259"/>
-      <c r="H38" s="259"/>
-      <c r="I38" s="259"/>
-      <c r="J38" s="275"/>
-      <c r="K38" s="259"/>
-      <c r="L38" s="259"/>
-      <c r="M38" s="263"/>
+      <c r="C38" s="251"/>
+      <c r="D38" s="251"/>
+      <c r="E38" s="251"/>
+      <c r="F38" s="250"/>
+      <c r="G38" s="251"/>
+      <c r="H38" s="251"/>
+      <c r="I38" s="251"/>
+      <c r="J38" s="258"/>
+      <c r="K38" s="251"/>
+      <c r="L38" s="251"/>
+      <c r="M38" s="259"/>
     </row>
     <row r="39" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B39" s="249" t="s">
+      <c r="B39" s="247" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="250"/>
-      <c r="D39" s="250"/>
-      <c r="E39" s="250"/>
-      <c r="F39" s="250"/>
-      <c r="G39" s="250"/>
-      <c r="H39" s="250"/>
-      <c r="I39" s="250"/>
-      <c r="J39" s="250"/>
-      <c r="K39" s="250"/>
-      <c r="L39" s="250"/>
-      <c r="M39" s="251"/>
+      <c r="C39" s="248"/>
+      <c r="D39" s="248"/>
+      <c r="E39" s="248"/>
+      <c r="F39" s="248"/>
+      <c r="G39" s="248"/>
+      <c r="H39" s="248"/>
+      <c r="I39" s="248"/>
+      <c r="J39" s="248"/>
+      <c r="K39" s="248"/>
+      <c r="L39" s="248"/>
+      <c r="M39" s="249"/>
     </row>
     <row r="40" spans="2:13" ht="19.5" customHeight="1">
       <c r="B40" s="122"/>
@@ -4642,6 +4630,41 @@
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="E9:M9"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="E11:M11"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B3:M4"/>
+    <mergeCell ref="E7:M7"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E12:M12"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="B39:M39"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="B21:D21"/>
@@ -4658,48 +4681,13 @@
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="J36:M36"/>
     <mergeCell ref="B34:M34"/>
-    <mergeCell ref="B3:M4"/>
-    <mergeCell ref="E7:M7"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E12:M12"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="E11:M11"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="E9:M9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:M10"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:AK58"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -4733,37 +4721,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="436" t="s">
+      <c r="B2" s="420" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="437"/>
-      <c r="D2" s="437"/>
-      <c r="E2" s="437"/>
-      <c r="F2" s="437"/>
-      <c r="G2" s="437"/>
-      <c r="H2" s="437"/>
-      <c r="I2" s="437"/>
-      <c r="J2" s="437"/>
-      <c r="K2" s="437"/>
-      <c r="L2" s="437"/>
-      <c r="M2" s="437"/>
-      <c r="N2" s="437"/>
-      <c r="O2" s="437"/>
-      <c r="P2" s="437"/>
-      <c r="Q2" s="437"/>
-      <c r="R2" s="437"/>
-      <c r="S2" s="437"/>
-      <c r="T2" s="437"/>
-      <c r="U2" s="437"/>
-      <c r="V2" s="437"/>
-      <c r="W2" s="437"/>
-      <c r="X2" s="437"/>
-      <c r="Y2" s="437"/>
-      <c r="Z2" s="437"/>
-      <c r="AA2" s="437"/>
-      <c r="AB2" s="437"/>
-      <c r="AC2" s="437"/>
-      <c r="AD2" s="437"/>
+      <c r="C2" s="421"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="421"/>
+      <c r="F2" s="421"/>
+      <c r="G2" s="421"/>
+      <c r="H2" s="421"/>
+      <c r="I2" s="421"/>
+      <c r="J2" s="421"/>
+      <c r="K2" s="421"/>
+      <c r="L2" s="421"/>
+      <c r="M2" s="421"/>
+      <c r="N2" s="421"/>
+      <c r="O2" s="421"/>
+      <c r="P2" s="421"/>
+      <c r="Q2" s="421"/>
+      <c r="R2" s="421"/>
+      <c r="S2" s="421"/>
+      <c r="T2" s="421"/>
+      <c r="U2" s="421"/>
+      <c r="V2" s="421"/>
+      <c r="W2" s="421"/>
+      <c r="X2" s="421"/>
+      <c r="Y2" s="421"/>
+      <c r="Z2" s="421"/>
+      <c r="AA2" s="421"/>
+      <c r="AB2" s="421"/>
+      <c r="AC2" s="421"/>
+      <c r="AD2" s="421"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -4890,39 +4878,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="428">
+      <c r="B10" s="438">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="424"/>
-      <c r="D10" s="424"/>
-      <c r="E10" s="424"/>
-      <c r="F10" s="424"/>
-      <c r="G10" s="424"/>
+      <c r="C10" s="423"/>
+      <c r="D10" s="423"/>
+      <c r="E10" s="423"/>
+      <c r="F10" s="423"/>
+      <c r="G10" s="423"/>
       <c r="H10" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="I10" s="445">
+      <c r="I10" s="437">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="424"/>
-      <c r="K10" s="424"/>
-      <c r="L10" s="424"/>
-      <c r="M10" s="424"/>
-      <c r="N10" s="424"/>
-      <c r="O10" s="424"/>
-      <c r="P10" s="424"/>
+      <c r="J10" s="423"/>
+      <c r="K10" s="423"/>
+      <c r="L10" s="423"/>
+      <c r="M10" s="423"/>
+      <c r="N10" s="423"/>
+      <c r="O10" s="423"/>
+      <c r="P10" s="423"/>
       <c r="Q10" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R10" s="423">
+      <c r="R10" s="422">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="424"/>
-      <c r="T10" s="424"/>
-      <c r="U10" s="424"/>
+      <c r="S10" s="423"/>
+      <c r="T10" s="423"/>
+      <c r="U10" s="423"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>239</v>
@@ -4957,13 +4945,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="423">
+      <c r="W11" s="422">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="424"/>
-      <c r="Y11" s="424"/>
-      <c r="Z11" s="424"/>
+      <c r="X11" s="423"/>
+      <c r="Y11" s="423"/>
+      <c r="Z11" s="423"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -4990,13 +4978,13 @@
       <c r="Q12" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R12" s="443">
+      <c r="R12" s="434">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="424"/>
-      <c r="T12" s="424"/>
-      <c r="U12" s="424"/>
+      <c r="S12" s="423"/>
+      <c r="T12" s="423"/>
+      <c r="U12" s="423"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -5016,10 +5004,10 @@
         <v>240</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="435"/>
-      <c r="X14" s="424"/>
-      <c r="Y14" s="424"/>
-      <c r="Z14" s="424"/>
+      <c r="W14" s="427"/>
+      <c r="X14" s="423"/>
+      <c r="Y14" s="423"/>
+      <c r="Z14" s="423"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -5045,38 +5033,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="440" t="s">
+      <c r="B16" s="431" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="424"/>
-      <c r="D16" s="424"/>
-      <c r="E16" s="424"/>
-      <c r="F16" s="424"/>
-      <c r="G16" s="424"/>
+      <c r="C16" s="423"/>
+      <c r="D16" s="423"/>
+      <c r="E16" s="423"/>
+      <c r="F16" s="423"/>
+      <c r="G16" s="423"/>
       <c r="H16" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="I16" s="430" t="str">
+      <c r="I16" s="440" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="424"/>
-      <c r="K16" s="424"/>
-      <c r="L16" s="424"/>
-      <c r="M16" s="424"/>
-      <c r="N16" s="424"/>
-      <c r="O16" s="424"/>
-      <c r="P16" s="424"/>
+      <c r="J16" s="423"/>
+      <c r="K16" s="423"/>
+      <c r="L16" s="423"/>
+      <c r="M16" s="423"/>
+      <c r="N16" s="423"/>
+      <c r="O16" s="423"/>
+      <c r="P16" s="423"/>
       <c r="Q16" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R16" s="435" t="str">
+      <c r="R16" s="427" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="424"/>
-      <c r="T16" s="424"/>
-      <c r="U16" s="424"/>
+      <c r="S16" s="423"/>
+      <c r="T16" s="423"/>
+      <c r="U16" s="423"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -5088,10 +5076,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="435"/>
-      <c r="X17" s="424"/>
-      <c r="Y17" s="424"/>
-      <c r="Z17" s="424"/>
+      <c r="W17" s="427"/>
+      <c r="X17" s="423"/>
+      <c r="Y17" s="423"/>
+      <c r="Z17" s="423"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -5115,13 +5103,13 @@
       <c r="Q18" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R18" s="434" t="str">
+      <c r="R18" s="443" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="424"/>
-      <c r="T18" s="424"/>
-      <c r="U18" s="424"/>
+      <c r="S18" s="423"/>
+      <c r="T18" s="423"/>
+      <c r="U18" s="423"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -5203,13 +5191,13 @@
       <c r="V22" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W22" s="444">
+      <c r="W22" s="435">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X22" s="427"/>
-      <c r="Y22" s="427"/>
-      <c r="Z22" s="427"/>
+      <c r="X22" s="430"/>
+      <c r="Y22" s="430"/>
+      <c r="Z22" s="430"/>
     </row>
     <row r="23" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B23" s="85" t="s">
@@ -5218,13 +5206,13 @@
       <c r="V23" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W23" s="426" t="str">
+      <c r="W23" s="429" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="X23" s="427"/>
-      <c r="Y23" s="427"/>
-      <c r="Z23" s="427"/>
+      <c r="X23" s="430"/>
+      <c r="Y23" s="430"/>
+      <c r="Z23" s="430"/>
     </row>
     <row r="24" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B24" s="86" t="s">
@@ -5233,13 +5221,13 @@
       <c r="V24" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W24" s="438">
+      <c r="W24" s="424">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="421"/>
-      <c r="Y24" s="421"/>
-      <c r="Z24" s="421"/>
+      <c r="X24" s="425"/>
+      <c r="Y24" s="425"/>
+      <c r="Z24" s="425"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -5248,13 +5236,13 @@
       <c r="V25" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W25" s="426">
+      <c r="W25" s="429">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H9</f>
         <v>0</v>
       </c>
-      <c r="X25" s="427"/>
-      <c r="Y25" s="427"/>
-      <c r="Z25" s="427"/>
+      <c r="X25" s="430"/>
+      <c r="Y25" s="430"/>
+      <c r="Z25" s="430"/>
     </row>
     <row r="26" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B26" s="85" t="s">
@@ -5263,13 +5251,13 @@
       <c r="V26" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W26" s="426">
+      <c r="W26" s="429">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H14</f>
         <v>0</v>
       </c>
-      <c r="X26" s="427"/>
-      <c r="Y26" s="427"/>
-      <c r="Z26" s="427"/>
+      <c r="X26" s="430"/>
+      <c r="Y26" s="430"/>
+      <c r="Z26" s="430"/>
     </row>
     <row r="27" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B27" s="85" t="s">
@@ -5278,13 +5266,13 @@
       <c r="V27" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W27" s="426">
+      <c r="W27" s="429">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H19</f>
         <v>0</v>
       </c>
-      <c r="X27" s="427"/>
-      <c r="Y27" s="427"/>
-      <c r="Z27" s="427"/>
+      <c r="X27" s="430"/>
+      <c r="Y27" s="430"/>
+      <c r="Z27" s="430"/>
     </row>
     <row r="28" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B28" s="85" t="s">
@@ -5293,13 +5281,13 @@
       <c r="V28" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W28" s="426">
+      <c r="W28" s="429">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H24</f>
         <v>0</v>
       </c>
-      <c r="X28" s="427"/>
-      <c r="Y28" s="427"/>
-      <c r="Z28" s="427"/>
+      <c r="X28" s="430"/>
+      <c r="Y28" s="430"/>
+      <c r="Z28" s="430"/>
     </row>
     <row r="29" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B29" s="85" t="s">
@@ -5308,13 +5296,13 @@
       <c r="V29" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W29" s="426">
+      <c r="W29" s="429">
         <f>'LAUDO DE AVALIAÇÃO 13'!G8</f>
         <v>0</v>
       </c>
-      <c r="X29" s="427"/>
-      <c r="Y29" s="427"/>
-      <c r="Z29" s="427"/>
+      <c r="X29" s="430"/>
+      <c r="Y29" s="430"/>
+      <c r="Z29" s="430"/>
     </row>
     <row r="30" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B30" s="86" t="s">
@@ -5323,13 +5311,13 @@
       <c r="V30" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W30" s="439">
+      <c r="W30" s="428">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="421"/>
-      <c r="Y30" s="421"/>
-      <c r="Z30" s="421"/>
+      <c r="X30" s="425"/>
+      <c r="Y30" s="425"/>
+      <c r="Z30" s="425"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -5339,83 +5327,83 @@
       <c r="V31" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="W31" s="442">
+      <c r="W31" s="433">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="421"/>
-      <c r="Y31" s="421"/>
-      <c r="Z31" s="421"/>
+      <c r="X31" s="425"/>
+      <c r="Y31" s="425"/>
+      <c r="Z31" s="425"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>254</v>
       </c>
-      <c r="K32" s="441">
+      <c r="K32" s="432">
         <v>43009</v>
       </c>
-      <c r="L32" s="427"/>
-      <c r="M32" s="427"/>
-      <c r="N32" s="427"/>
-      <c r="O32" s="427"/>
-      <c r="P32" s="427"/>
-      <c r="Q32" s="427"/>
-      <c r="R32" s="427"/>
-      <c r="S32" s="427"/>
-      <c r="T32" s="427"/>
-      <c r="U32" s="427"/>
-      <c r="V32" s="427"/>
-      <c r="W32" s="427"/>
-      <c r="X32" s="427"/>
-      <c r="Y32" s="427"/>
-      <c r="Z32" s="427"/>
+      <c r="L32" s="430"/>
+      <c r="M32" s="430"/>
+      <c r="N32" s="430"/>
+      <c r="O32" s="430"/>
+      <c r="P32" s="430"/>
+      <c r="Q32" s="430"/>
+      <c r="R32" s="430"/>
+      <c r="S32" s="430"/>
+      <c r="T32" s="430"/>
+      <c r="U32" s="430"/>
+      <c r="V32" s="430"/>
+      <c r="W32" s="430"/>
+      <c r="X32" s="430"/>
+      <c r="Y32" s="430"/>
+      <c r="Z32" s="430"/>
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="420" t="s">
+      <c r="O33" s="444" t="s">
         <v>255</v>
       </c>
-      <c r="P33" s="421"/>
-      <c r="Q33" s="421"/>
-      <c r="R33" s="421"/>
-      <c r="S33" s="421"/>
-      <c r="T33" s="421"/>
-      <c r="U33" s="421"/>
-      <c r="V33" s="421"/>
-      <c r="W33" s="425" t="s">
+      <c r="P33" s="425"/>
+      <c r="Q33" s="425"/>
+      <c r="R33" s="425"/>
+      <c r="S33" s="425"/>
+      <c r="T33" s="425"/>
+      <c r="U33" s="425"/>
+      <c r="V33" s="425"/>
+      <c r="W33" s="445" t="s">
         <v>256</v>
       </c>
-      <c r="X33" s="329"/>
-      <c r="Y33" s="329"/>
-      <c r="Z33" s="329"/>
-      <c r="AA33" s="329"/>
-      <c r="AB33" s="329"/>
-      <c r="AC33" s="329"/>
-      <c r="AD33" s="329"/>
+      <c r="X33" s="333"/>
+      <c r="Y33" s="333"/>
+      <c r="Z33" s="333"/>
+      <c r="AA33" s="333"/>
+      <c r="AB33" s="333"/>
+      <c r="AC33" s="333"/>
+      <c r="AD33" s="333"/>
       <c r="AG33" s="89"/>
     </row>
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="432">
+      <c r="Q34" s="436">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
-      <c r="R34" s="427"/>
-      <c r="S34" s="427"/>
-      <c r="T34" s="427"/>
+      <c r="R34" s="430"/>
+      <c r="S34" s="430"/>
+      <c r="T34" s="430"/>
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="432">
+      <c r="Y34" s="436">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
-      <c r="Z34" s="427"/>
-      <c r="AA34" s="427"/>
-      <c r="AB34" s="427"/>
+      <c r="Z34" s="430"/>
+      <c r="AA34" s="430"/>
+      <c r="AB34" s="430"/>
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AG34" s="86"/>
@@ -5478,32 +5466,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="429"/>
-      <c r="C38" s="424"/>
+      <c r="B38" s="426"/>
+      <c r="C38" s="423"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="429"/>
-      <c r="C39" s="424"/>
+      <c r="B39" s="426"/>
+      <c r="C39" s="423"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="429"/>
-      <c r="C40" s="424"/>
+      <c r="B40" s="426"/>
+      <c r="C40" s="423"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="429"/>
-      <c r="C41" s="424"/>
+      <c r="B41" s="426"/>
+      <c r="C41" s="423"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="429"/>
-      <c r="C42" s="424"/>
+      <c r="B42" s="426"/>
+      <c r="C42" s="423"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="429"/>
-      <c r="C43" s="424"/>
+      <c r="B43" s="426"/>
+      <c r="C43" s="423"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="429"/>
-      <c r="C44" s="424"/>
+      <c r="B44" s="426"/>
+      <c r="C44" s="423"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -5574,10 +5562,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="433"/>
-      <c r="F49" s="424"/>
-      <c r="G49" s="424"/>
-      <c r="H49" s="424"/>
+      <c r="E49" s="442"/>
+      <c r="F49" s="423"/>
+      <c r="G49" s="423"/>
+      <c r="H49" s="423"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -5600,44 +5588,66 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="422"/>
-      <c r="I52" s="329"/>
-      <c r="J52" s="329"/>
-      <c r="K52" s="329"/>
-      <c r="L52" s="329"/>
-      <c r="M52" s="329"/>
-      <c r="N52" s="329"/>
-      <c r="O52" s="329"/>
-      <c r="P52" s="329"/>
+      <c r="H52" s="439"/>
+      <c r="I52" s="333"/>
+      <c r="J52" s="333"/>
+      <c r="K52" s="333"/>
+      <c r="L52" s="333"/>
+      <c r="M52" s="333"/>
+      <c r="N52" s="333"/>
+      <c r="O52" s="333"/>
+      <c r="P52" s="333"/>
     </row>
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="431"/>
-      <c r="I55" s="329"/>
-      <c r="J55" s="329"/>
-      <c r="K55" s="329"/>
-      <c r="L55" s="329"/>
-      <c r="M55" s="329"/>
-      <c r="N55" s="329"/>
-      <c r="O55" s="329"/>
-      <c r="P55" s="329"/>
+      <c r="H55" s="441"/>
+      <c r="I55" s="333"/>
+      <c r="J55" s="333"/>
+      <c r="K55" s="333"/>
+      <c r="L55" s="333"/>
+      <c r="M55" s="333"/>
+      <c r="N55" s="333"/>
+      <c r="O55" s="333"/>
+      <c r="P55" s="333"/>
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="422"/>
-      <c r="I57" s="329"/>
-      <c r="J57" s="329"/>
-      <c r="K57" s="329"/>
-      <c r="L57" s="329"/>
-      <c r="M57" s="329"/>
-      <c r="N57" s="329"/>
-      <c r="O57" s="329"/>
-      <c r="P57" s="329"/>
+      <c r="H57" s="439"/>
+      <c r="I57" s="333"/>
+      <c r="J57" s="333"/>
+      <c r="K57" s="333"/>
+      <c r="L57" s="333"/>
+      <c r="M57" s="333"/>
+      <c r="N57" s="333"/>
+      <c r="O57" s="333"/>
+      <c r="P57" s="333"/>
     </row>
     <row r="58" spans="5:16" ht="6.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="O33:V33"/>
+    <mergeCell ref="H52:P52"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="W33:AD33"/>
+    <mergeCell ref="W29:Z29"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="H57:P57"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="I16:P16"/>
+    <mergeCell ref="W25:Z25"/>
+    <mergeCell ref="H55:P55"/>
+    <mergeCell ref="Q34:T34"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="R18:U18"/>
+    <mergeCell ref="W14:Z14"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="W28:Z28"/>
+    <mergeCell ref="W27:Z27"/>
+    <mergeCell ref="W17:Z17"/>
     <mergeCell ref="B2:AD2"/>
     <mergeCell ref="R10:U10"/>
     <mergeCell ref="W24:Z24"/>
@@ -5654,28 +5664,6 @@
     <mergeCell ref="W22:Z22"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="I10:P10"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="H57:P57"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="I16:P16"/>
-    <mergeCell ref="W25:Z25"/>
-    <mergeCell ref="H55:P55"/>
-    <mergeCell ref="Q34:T34"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="W14:Z14"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="W28:Z28"/>
-    <mergeCell ref="W27:Z27"/>
-    <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="O33:V33"/>
-    <mergeCell ref="H52:P52"/>
-    <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="W33:AD33"/>
-    <mergeCell ref="W29:Z29"/>
-    <mergeCell ref="W23:Z23"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:G10 B16:G16">
     <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
@@ -5694,7 +5682,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B1:L24"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -5711,24 +5699,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="461" t="s">
+      <c r="B1" s="452" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="462"/>
-      <c r="D1" s="462"/>
-      <c r="E1" s="462"/>
-      <c r="F1" s="462"/>
-      <c r="G1" s="462"/>
-      <c r="H1" s="463"/>
+      <c r="C1" s="453"/>
+      <c r="D1" s="453"/>
+      <c r="E1" s="453"/>
+      <c r="F1" s="453"/>
+      <c r="G1" s="453"/>
+      <c r="H1" s="454"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="458"/>
-      <c r="C2" s="459"/>
-      <c r="D2" s="459"/>
-      <c r="E2" s="459"/>
-      <c r="F2" s="459"/>
-      <c r="G2" s="459"/>
-      <c r="H2" s="460"/>
+      <c r="B2" s="448"/>
+      <c r="C2" s="449"/>
+      <c r="D2" s="449"/>
+      <c r="E2" s="449"/>
+      <c r="F2" s="449"/>
+      <c r="G2" s="449"/>
+      <c r="H2" s="450"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -5763,32 +5751,32 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="451" t="s">
+      <c r="B6" s="457" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="453" t="s">
+      <c r="C6" s="459" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="449" t="s">
+      <c r="D6" s="461" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="455" t="s">
+      <c r="E6" s="462" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="455" t="s">
+      <c r="F6" s="462" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="446" t="s">
+      <c r="G6" s="455" t="s">
         <v>264</v>
       </c>
-      <c r="H6" s="447"/>
+      <c r="H6" s="456"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="452"/>
-      <c r="C7" s="450"/>
-      <c r="D7" s="450"/>
-      <c r="E7" s="263"/>
-      <c r="F7" s="263"/>
+      <c r="B7" s="458"/>
+      <c r="C7" s="460"/>
+      <c r="D7" s="460"/>
+      <c r="E7" s="259"/>
+      <c r="F7" s="259"/>
       <c r="G7" s="47" t="s">
         <v>265</v>
       </c>
@@ -5809,14 +5797,14 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="448" t="s">
+      <c r="B9" s="463" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="250"/>
-      <c r="D9" s="250"/>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="251"/>
+      <c r="C9" s="248"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="249"/>
       <c r="H9" s="59">
         <f>TRUNC(SUM(H8:H8),2)</f>
         <v>0</v>
@@ -5834,32 +5822,32 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="451" t="s">
+      <c r="B11" s="457" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="453" t="s">
+      <c r="C11" s="459" t="s">
         <v>260</v>
       </c>
-      <c r="D11" s="449" t="s">
+      <c r="D11" s="461" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="454" t="s">
+      <c r="E11" s="451" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="454" t="s">
+      <c r="F11" s="451" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="446" t="s">
+      <c r="G11" s="455" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="447"/>
+      <c r="H11" s="456"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="452"/>
-      <c r="C12" s="450"/>
-      <c r="D12" s="450"/>
-      <c r="E12" s="263"/>
-      <c r="F12" s="263"/>
+      <c r="B12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="259"/>
+      <c r="F12" s="259"/>
       <c r="G12" s="47" t="s">
         <v>265</v>
       </c>
@@ -5880,14 +5868,14 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="448" t="s">
+      <c r="B14" s="463" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="250"/>
-      <c r="D14" s="250"/>
-      <c r="E14" s="250"/>
-      <c r="F14" s="250"/>
-      <c r="G14" s="251"/>
+      <c r="C14" s="248"/>
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="248"/>
+      <c r="G14" s="249"/>
       <c r="H14" s="63">
         <f>TRUNC(SUM(H13:H13),2)</f>
         <v>0</v>
@@ -5905,32 +5893,32 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="451" t="s">
+      <c r="B16" s="457" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="453" t="s">
+      <c r="C16" s="459" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="449" t="s">
+      <c r="D16" s="461" t="s">
         <v>261</v>
       </c>
-      <c r="E16" s="454" t="s">
+      <c r="E16" s="451" t="s">
         <v>267</v>
       </c>
-      <c r="F16" s="454" t="s">
+      <c r="F16" s="451" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="446" t="s">
+      <c r="G16" s="455" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="447"/>
+      <c r="H16" s="456"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="452"/>
-      <c r="C17" s="450"/>
-      <c r="D17" s="450"/>
-      <c r="E17" s="263"/>
-      <c r="F17" s="263"/>
+      <c r="B17" s="458"/>
+      <c r="C17" s="460"/>
+      <c r="D17" s="460"/>
+      <c r="E17" s="259"/>
+      <c r="F17" s="259"/>
       <c r="G17" s="22" t="s">
         <v>265</v>
       </c>
@@ -5953,14 +5941,14 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="448" t="s">
+      <c r="B19" s="463" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="250"/>
-      <c r="D19" s="250"/>
-      <c r="E19" s="250"/>
-      <c r="F19" s="250"/>
-      <c r="G19" s="251"/>
+      <c r="C19" s="248"/>
+      <c r="D19" s="248"/>
+      <c r="E19" s="248"/>
+      <c r="F19" s="248"/>
+      <c r="G19" s="249"/>
       <c r="H19" s="64">
         <f>TRUNC(SUM(H18:H18),2)</f>
         <v>0</v>
@@ -5978,32 +5966,32 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="451" t="s">
+      <c r="B21" s="457" t="s">
         <v>259</v>
       </c>
-      <c r="C21" s="453" t="s">
+      <c r="C21" s="459" t="s">
         <v>260</v>
       </c>
-      <c r="D21" s="449" t="s">
+      <c r="D21" s="461" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="454" t="s">
+      <c r="E21" s="451" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="454" t="s">
+      <c r="F21" s="451" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="446" t="s">
+      <c r="G21" s="455" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="447"/>
+      <c r="H21" s="456"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="452"/>
-      <c r="C22" s="450"/>
-      <c r="D22" s="450"/>
-      <c r="E22" s="263"/>
-      <c r="F22" s="263"/>
+      <c r="B22" s="458"/>
+      <c r="C22" s="460"/>
+      <c r="D22" s="460"/>
+      <c r="E22" s="259"/>
+      <c r="F22" s="259"/>
       <c r="G22" s="47" t="s">
         <v>265</v>
       </c>
@@ -6024,18 +6012,32 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="456" t="s">
+      <c r="B24" s="446" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="457"/>
-      <c r="D24" s="457"/>
-      <c r="E24" s="457"/>
-      <c r="F24" s="457"/>
-      <c r="G24" s="393"/>
+      <c r="C24" s="447"/>
+      <c r="D24" s="447"/>
+      <c r="E24" s="447"/>
+      <c r="F24" s="447"/>
+      <c r="G24" s="396"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="E16:E17"/>
@@ -6052,20 +6054,6 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="F21:F22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -6075,7 +6063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B1:M8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -6094,11 +6082,11 @@
       <c r="B1" s="466" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="459"/>
-      <c r="D1" s="459"/>
-      <c r="E1" s="459"/>
-      <c r="F1" s="459"/>
-      <c r="G1" s="459"/>
+      <c r="C1" s="449"/>
+      <c r="D1" s="449"/>
+      <c r="E1" s="449"/>
+      <c r="F1" s="449"/>
+      <c r="G1" s="449"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -6125,11 +6113,11 @@
       <c r="B4" s="467" t="s">
         <v>272</v>
       </c>
-      <c r="C4" s="250"/>
-      <c r="D4" s="250"/>
-      <c r="E4" s="250"/>
-      <c r="F4" s="250"/>
-      <c r="G4" s="251"/>
+      <c r="C4" s="248"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="249"/>
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
@@ -6148,14 +6136,14 @@
       <c r="F5" s="465" t="s">
         <v>277</v>
       </c>
-      <c r="G5" s="250"/>
+      <c r="G5" s="248"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="263"/>
-      <c r="C6" s="450"/>
-      <c r="D6" s="450"/>
-      <c r="E6" s="450"/>
+      <c r="B6" s="259"/>
+      <c r="C6" s="460"/>
+      <c r="D6" s="460"/>
+      <c r="E6" s="460"/>
       <c r="F6" s="30" t="s">
         <v>265</v>
       </c>
@@ -6198,7 +6186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -6207,151 +6195,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="474" t="s">
+      <c r="A1" s="476" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="248"/>
-      <c r="E1" s="248"/>
-      <c r="F1" s="248"/>
-      <c r="G1" s="248"/>
-      <c r="H1" s="248"/>
-      <c r="I1" s="248"/>
-      <c r="J1" s="248"/>
-      <c r="K1" s="248"/>
-      <c r="L1" s="248"/>
-      <c r="M1" s="248"/>
-      <c r="N1" s="248"/>
-      <c r="O1" s="475"/>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="248"/>
-      <c r="S1" s="248"/>
+      <c r="B1" s="253"/>
+      <c r="C1" s="253"/>
+      <c r="D1" s="253"/>
+      <c r="E1" s="253"/>
+      <c r="F1" s="253"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="253"/>
+      <c r="K1" s="253"/>
+      <c r="L1" s="253"/>
+      <c r="M1" s="253"/>
+      <c r="N1" s="253"/>
+      <c r="O1" s="469"/>
+      <c r="P1" s="253"/>
+      <c r="Q1" s="253"/>
+      <c r="R1" s="253"/>
+      <c r="S1" s="253"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="476" t="s">
+      <c r="A2" s="474" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="476" t="s">
+      <c r="B2" s="253"/>
+      <c r="C2" s="474" t="s">
         <v>278</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="248"/>
-      <c r="I2" s="248"/>
-      <c r="J2" s="472" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="475" t="s">
         <v>279</v>
       </c>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="M2" s="248"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="473" t="s">
+      <c r="A3" s="471" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="473" t="s">
+      <c r="B3" s="253"/>
+      <c r="C3" s="471" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="248"/>
-      <c r="H3" s="248"/>
-      <c r="I3" s="248"/>
-      <c r="J3" s="473" t="s">
+      <c r="D3" s="253"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="471" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="M3" s="248"/>
-      <c r="N3" s="248"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="253"/>
+      <c r="N3" s="253"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="473" t="s">
+      <c r="A4" s="471" t="s">
         <v>282</v>
       </c>
-      <c r="B4" s="248"/>
-      <c r="C4" s="473" t="s">
+      <c r="B4" s="253"/>
+      <c r="C4" s="471" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="471"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="M4" s="248"/>
-      <c r="N4" s="248"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="473"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
+      <c r="M4" s="253"/>
+      <c r="N4" s="253"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="473" t="s">
+      <c r="A5" s="471" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="248"/>
-      <c r="C5" s="473" t="s">
+      <c r="B5" s="253"/>
+      <c r="C5" s="471" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="471"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="M5" s="248"/>
-      <c r="N5" s="248"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="473"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="M5" s="253"/>
+      <c r="N5" s="253"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="473" t="s">
+      <c r="A6" s="471" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="248"/>
-      <c r="C6" s="473" t="s">
+      <c r="B6" s="253"/>
+      <c r="C6" s="471" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
-      <c r="F6" s="248"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="248"/>
-      <c r="I6" s="248"/>
-      <c r="J6" s="473" t="s">
+      <c r="D6" s="253"/>
+      <c r="E6" s="253"/>
+      <c r="F6" s="253"/>
+      <c r="G6" s="253"/>
+      <c r="H6" s="253"/>
+      <c r="I6" s="253"/>
+      <c r="J6" s="471" t="s">
         <v>286</v>
       </c>
-      <c r="K6" s="248"/>
-      <c r="L6" s="248"/>
-      <c r="M6" s="248"/>
-      <c r="N6" s="248"/>
+      <c r="K6" s="253"/>
+      <c r="L6" s="253"/>
+      <c r="M6" s="253"/>
+      <c r="N6" s="253"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
       <c r="A7" s="470" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="248"/>
-      <c r="C7" s="248"/>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="248"/>
-      <c r="H7" s="248"/>
-      <c r="I7" s="248"/>
-      <c r="J7" s="248"/>
-      <c r="K7" s="248"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="248"/>
-      <c r="N7" s="248"/>
+      <c r="B7" s="253"/>
+      <c r="C7" s="253"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253"/>
+      <c r="F7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="253"/>
+      <c r="I7" s="253"/>
+      <c r="J7" s="253"/>
+      <c r="K7" s="253"/>
+      <c r="L7" s="253"/>
+      <c r="M7" s="253"/>
+      <c r="N7" s="253"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1"/>
     <row r="9" spans="1:19" ht="15" customHeight="1"/>
@@ -6380,120 +6368,138 @@
       <c r="A31" s="470" t="s">
         <v>288</v>
       </c>
-      <c r="B31" s="248"/>
-      <c r="C31" s="248"/>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
-      <c r="M31" s="248"/>
-      <c r="N31" s="248"/>
+      <c r="B31" s="253"/>
+      <c r="C31" s="253"/>
+      <c r="D31" s="253"/>
+      <c r="E31" s="253"/>
+      <c r="F31" s="253"/>
+      <c r="G31" s="253"/>
+      <c r="H31" s="253"/>
+      <c r="I31" s="253"/>
+      <c r="J31" s="253"/>
+      <c r="K31" s="253"/>
+      <c r="L31" s="253"/>
+      <c r="M31" s="253"/>
+      <c r="N31" s="253"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
-      <c r="A32" s="469" t="s">
+      <c r="A32" s="472" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="248"/>
-      <c r="C32" s="248"/>
-      <c r="D32" s="469" t="s">
+      <c r="B32" s="253"/>
+      <c r="C32" s="253"/>
+      <c r="D32" s="472" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="248"/>
-      <c r="F32" s="248"/>
-      <c r="G32" s="469" t="s">
+      <c r="E32" s="253"/>
+      <c r="F32" s="253"/>
+      <c r="G32" s="472" t="s">
         <v>289</v>
       </c>
-      <c r="H32" s="248"/>
-      <c r="I32" s="248"/>
-      <c r="J32" s="469" t="s">
+      <c r="H32" s="253"/>
+      <c r="I32" s="253"/>
+      <c r="J32" s="472" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="248"/>
-      <c r="L32" s="248"/>
-      <c r="M32" s="248"/>
+      <c r="K32" s="253"/>
+      <c r="L32" s="253"/>
+      <c r="M32" s="253"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
-      <c r="A33" s="469" t="s">
+      <c r="A33" s="472" t="s">
         <v>290</v>
       </c>
-      <c r="B33" s="248"/>
-      <c r="C33" s="248"/>
-      <c r="D33" s="469" t="s">
+      <c r="B33" s="253"/>
+      <c r="C33" s="253"/>
+      <c r="D33" s="472" t="s">
         <v>291</v>
       </c>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="469" t="s">
+      <c r="E33" s="253"/>
+      <c r="F33" s="253"/>
+      <c r="G33" s="472" t="s">
         <v>292</v>
       </c>
-      <c r="H33" s="248"/>
-      <c r="I33" s="248"/>
-      <c r="J33" s="469" t="s">
+      <c r="H33" s="253"/>
+      <c r="I33" s="253"/>
+      <c r="J33" s="472" t="s">
         <v>293</v>
       </c>
-      <c r="K33" s="248"/>
-      <c r="L33" s="248"/>
-      <c r="M33" s="248"/>
+      <c r="K33" s="253"/>
+      <c r="L33" s="253"/>
+      <c r="M33" s="253"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="470" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="248"/>
-      <c r="C34" s="248"/>
-      <c r="D34" s="248"/>
-      <c r="E34" s="248"/>
-      <c r="F34" s="248"/>
-      <c r="G34" s="248"/>
-      <c r="H34" s="248"/>
-      <c r="I34" s="248"/>
-      <c r="J34" s="248"/>
-      <c r="K34" s="248"/>
-      <c r="L34" s="248"/>
-      <c r="M34" s="248"/>
-      <c r="N34" s="248"/>
+      <c r="B34" s="253"/>
+      <c r="C34" s="253"/>
+      <c r="D34" s="253"/>
+      <c r="E34" s="253"/>
+      <c r="F34" s="253"/>
+      <c r="G34" s="253"/>
+      <c r="H34" s="253"/>
+      <c r="I34" s="253"/>
+      <c r="J34" s="253"/>
+      <c r="K34" s="253"/>
+      <c r="L34" s="253"/>
+      <c r="M34" s="253"/>
+      <c r="N34" s="253"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="469" t="s">
+      <c r="A35" s="472" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="248"/>
-      <c r="C35" s="248"/>
-      <c r="F35" s="469" t="s">
+      <c r="B35" s="253"/>
+      <c r="C35" s="253"/>
+      <c r="F35" s="472" t="s">
         <v>294</v>
       </c>
-      <c r="G35" s="248"/>
-      <c r="H35" s="248"/>
-      <c r="K35" s="469" t="s">
+      <c r="G35" s="253"/>
+      <c r="H35" s="253"/>
+      <c r="K35" s="472" t="s">
         <v>295</v>
       </c>
-      <c r="L35" s="248"/>
-      <c r="M35" s="248"/>
+      <c r="L35" s="253"/>
+      <c r="M35" s="253"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
-      <c r="A36" s="469" t="s">
+      <c r="A36" s="472" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="248"/>
-      <c r="C36" s="248"/>
-      <c r="F36" s="469" t="s">
+      <c r="B36" s="253"/>
+      <c r="C36" s="253"/>
+      <c r="F36" s="472" t="s">
         <v>296</v>
       </c>
-      <c r="G36" s="248"/>
-      <c r="H36" s="248"/>
-      <c r="K36" s="469" t="s">
+      <c r="G36" s="253"/>
+      <c r="H36" s="253"/>
+      <c r="K36" s="472" t="s">
         <v>297</v>
       </c>
-      <c r="L36" s="248"/>
-      <c r="M36" s="248"/>
+      <c r="L36" s="253"/>
+      <c r="M36" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A31:N31"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="C6:I6"/>
@@ -6510,24 +6516,6 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="K36:M36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6535,7 +6523,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="D8:L47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -6904,7 +6892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -7178,24 +7166,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:I19"/>
@@ -7205,6 +7175,24 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7212,7 +7200,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="C2:T21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -7253,7 +7241,7 @@
       <c r="T3" s="207"/>
     </row>
     <row r="4" spans="3:20">
-      <c r="C4" s="316" t="str">
+      <c r="C4" s="290" t="str">
         <f>C16</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -7282,22 +7270,22 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="314" t="s">
+      <c r="C5" s="306" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="263"/>
-      <c r="E5" s="314" t="s">
+      <c r="D5" s="259"/>
+      <c r="E5" s="306" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="263"/>
-      <c r="G5" s="314" t="s">
+      <c r="F5" s="259"/>
+      <c r="G5" s="306" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="263"/>
-      <c r="I5" s="307" t="s">
+      <c r="H5" s="259"/>
+      <c r="I5" s="301" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="263"/>
+      <c r="J5" s="259"/>
       <c r="L5" s="207"/>
       <c r="M5" s="207"/>
       <c r="N5" s="207" t="s">
@@ -7315,19 +7303,19 @@
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="D6" s="251"/>
-      <c r="E6" s="313" t="s">
+      <c r="D6" s="249"/>
+      <c r="E6" s="296" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="251"/>
-      <c r="G6" s="315" t="s">
+      <c r="F6" s="249"/>
+      <c r="G6" s="294" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="251"/>
-      <c r="I6" s="291" t="s">
+      <c r="H6" s="249"/>
+      <c r="I6" s="308" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="251"/>
+      <c r="J6" s="249"/>
       <c r="L6" s="207">
         <v>231.63</v>
       </c>
@@ -7347,16 +7335,16 @@
       <c r="T6" s="207"/>
     </row>
     <row r="7" spans="3:20">
-      <c r="C7" s="312" t="s">
+      <c r="C7" s="291" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="250"/>
-      <c r="E7" s="250"/>
-      <c r="F7" s="250"/>
-      <c r="G7" s="250"/>
-      <c r="H7" s="250"/>
-      <c r="I7" s="250"/>
-      <c r="J7" s="251"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="248"/>
+      <c r="I7" s="248"/>
+      <c r="J7" s="249"/>
       <c r="L7" s="207"/>
       <c r="M7" s="207"/>
       <c r="N7" s="207"/>
@@ -7373,22 +7361,22 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="292" t="s">
+      <c r="C8" s="295" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="251"/>
-      <c r="E8" s="292" t="s">
+      <c r="D8" s="249"/>
+      <c r="E8" s="295" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="251"/>
-      <c r="G8" s="292" t="s">
+      <c r="F8" s="249"/>
+      <c r="G8" s="295" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="251"/>
-      <c r="I8" s="311" t="s">
+      <c r="H8" s="249"/>
+      <c r="I8" s="305" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="251"/>
+      <c r="J8" s="249"/>
       <c r="L8" s="207"/>
       <c r="M8" s="207"/>
       <c r="N8" s="207"/>
@@ -7400,22 +7388,22 @@
       <c r="T8" s="207"/>
     </row>
     <row r="9" spans="3:20">
-      <c r="C9" s="313">
+      <c r="C9" s="296">
         <v>52.034300000000002</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="E9" s="315" t="s">
+      <c r="D9" s="249"/>
+      <c r="E9" s="294" t="s">
         <v>303</v>
       </c>
-      <c r="F9" s="251"/>
+      <c r="F9" s="249"/>
       <c r="G9" s="293">
         <v>80</v>
       </c>
-      <c r="H9" s="251"/>
-      <c r="I9" s="291">
+      <c r="H9" s="249"/>
+      <c r="I9" s="308">
         <v>0.65039999999999998</v>
       </c>
-      <c r="J9" s="251"/>
+      <c r="J9" s="249"/>
       <c r="L9" s="207"/>
       <c r="M9" s="207"/>
       <c r="N9" s="207"/>
@@ -7427,16 +7415,16 @@
       <c r="T9" s="207"/>
     </row>
     <row r="10" spans="3:20">
-      <c r="C10" s="312" t="s">
+      <c r="C10" s="291" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="250"/>
-      <c r="E10" s="250"/>
-      <c r="F10" s="250"/>
-      <c r="G10" s="250"/>
-      <c r="H10" s="250"/>
-      <c r="I10" s="250"/>
-      <c r="J10" s="251"/>
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="248"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="248"/>
+      <c r="I10" s="248"/>
+      <c r="J10" s="249"/>
       <c r="L10" s="207"/>
       <c r="M10" s="207"/>
       <c r="N10" s="207"/>
@@ -7448,156 +7436,187 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="292" t="s">
+      <c r="C11" s="295" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="292" t="s">
+      <c r="D11" s="249"/>
+      <c r="E11" s="295" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="251"/>
-      <c r="G11" s="292" t="s">
+      <c r="F11" s="249"/>
+      <c r="G11" s="295" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="251"/>
-      <c r="I11" s="311" t="s">
+      <c r="H11" s="249"/>
+      <c r="I11" s="305" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="251"/>
+      <c r="J11" s="249"/>
     </row>
     <row r="12" spans="3:20">
-      <c r="C12" s="313">
+      <c r="C12" s="296">
         <v>52.034300000000002</v>
       </c>
-      <c r="D12" s="251"/>
-      <c r="E12" s="313">
+      <c r="D12" s="249"/>
+      <c r="E12" s="296">
         <v>18.2121</v>
       </c>
-      <c r="F12" s="251"/>
-      <c r="G12" s="315">
+      <c r="F12" s="249"/>
+      <c r="G12" s="294">
         <v>1.7411000000000001</v>
       </c>
-      <c r="H12" s="251"/>
-      <c r="I12" s="318">
+      <c r="H12" s="249"/>
+      <c r="I12" s="297">
         <v>9.7928999999999995</v>
       </c>
-      <c r="J12" s="251"/>
+      <c r="J12" s="249"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="292" t="s">
+      <c r="C13" s="295" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="E13" s="315" t="s">
+      <c r="D13" s="249"/>
+      <c r="E13" s="294" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="251"/>
-      <c r="G13" s="292" t="s">
+      <c r="F13" s="249"/>
+      <c r="G13" s="295" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="251"/>
-      <c r="I13" s="291" t="s">
+      <c r="H13" s="249"/>
+      <c r="I13" s="308" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="251"/>
+      <c r="J13" s="249"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="308" t="s">
+      <c r="C16" s="302" t="s">
         <v>302</v>
       </c>
-      <c r="D16" s="309"/>
-      <c r="E16" s="309"/>
-      <c r="F16" s="309"/>
-      <c r="G16" s="309"/>
-      <c r="H16" s="309"/>
-      <c r="I16" s="310"/>
+      <c r="D16" s="303"/>
+      <c r="E16" s="303"/>
+      <c r="F16" s="303"/>
+      <c r="G16" s="303"/>
+      <c r="H16" s="303"/>
+      <c r="I16" s="304"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="312" t="s">
+      <c r="C17" s="291" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="250"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="312" t="s">
+      <c r="D17" s="248"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="291" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="251"/>
-      <c r="H17" s="312" t="s">
+      <c r="G17" s="249"/>
+      <c r="H17" s="291" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="251"/>
+      <c r="I17" s="249"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="299" t="s">
+      <c r="C18" s="314" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="300"/>
-      <c r="E18" s="301"/>
-      <c r="F18" s="303">
+      <c r="D18" s="315"/>
+      <c r="E18" s="316"/>
+      <c r="F18" s="318">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="304"/>
-      <c r="H18" s="305">
+      <c r="G18" s="319"/>
+      <c r="H18" s="320">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="306"/>
+      <c r="I18" s="321"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="302" t="s">
+      <c r="C19" s="317" t="s">
         <v>301</v>
       </c>
-      <c r="D19" s="250"/>
-      <c r="E19" s="251"/>
+      <c r="D19" s="248"/>
+      <c r="E19" s="249"/>
       <c r="F19" s="293">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
-      <c r="G19" s="251"/>
-      <c r="H19" s="290">
+      <c r="G19" s="249"/>
+      <c r="H19" s="307">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="I19" s="251"/>
+      <c r="I19" s="249"/>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="319" t="s">
+      <c r="C20" s="298" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="320"/>
-      <c r="E20" s="321"/>
-      <c r="F20" s="297">
+      <c r="D20" s="299"/>
+      <c r="E20" s="300"/>
+      <c r="F20" s="312">
         <f>AMOSTRAS!E13</f>
         <v>19.953199999999999</v>
       </c>
-      <c r="G20" s="298"/>
-      <c r="H20" s="295">
+      <c r="G20" s="313"/>
+      <c r="H20" s="310">
         <f>AMOSTRAS!F13</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="I20" s="296"/>
+      <c r="I20" s="311"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="294" t="s">
+      <c r="C21" s="309" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="E21" s="251"/>
-      <c r="F21" s="317">
+      <c r="D21" s="248"/>
+      <c r="E21" s="249"/>
+      <c r="F21" s="292">
         <f>SUM(F18:G20)</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G21" s="251"/>
-      <c r="H21" s="290">
+      <c r="G21" s="249"/>
+      <c r="H21" s="307">
         <f>SUM(H18:I20)</f>
         <v>1</v>
       </c>
-      <c r="I21" s="251"/>
+      <c r="I21" s="249"/>
       <c r="J21" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="F21:G21"/>
@@ -7614,37 +7633,6 @@
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7652,7 +7640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:N112"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -7672,38 +7660,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="381" t="s">
+      <c r="B3" s="353" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="382"/>
-      <c r="D3" s="382"/>
-      <c r="E3" s="382"/>
-      <c r="F3" s="382"/>
-      <c r="G3" s="382"/>
-      <c r="H3" s="382"/>
-      <c r="I3" s="382"/>
-      <c r="L3" s="322" t="s">
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
+      <c r="H3" s="354"/>
+      <c r="I3" s="354"/>
+      <c r="L3" s="386" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="251"/>
+      <c r="M3" s="249"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1">
-      <c r="B4" s="328" t="s">
+      <c r="B4" s="332" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="329"/>
-      <c r="D4" s="329"/>
-      <c r="E4" s="340" t="s">
+      <c r="C4" s="333"/>
+      <c r="D4" s="333"/>
+      <c r="E4" s="388" t="s">
         <v>298</v>
       </c>
       <c r="F4" s="284"/>
       <c r="G4" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="383" t="s">
+      <c r="H4" s="355" t="s">
         <v>299</v>
       </c>
-      <c r="I4" s="253"/>
+      <c r="I4" s="263"/>
       <c r="J4" s="186"/>
       <c r="L4" s="153" t="s">
         <v>88</v>
@@ -7714,22 +7702,22 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
-      <c r="B5" s="331" t="s">
+      <c r="B5" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C5" s="284"/>
       <c r="D5" s="284"/>
-      <c r="E5" s="323" t="s">
+      <c r="E5" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F5" s="284"/>
       <c r="G5" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="364" t="s">
+      <c r="H5" s="374" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="253"/>
+      <c r="I5" s="263"/>
       <c r="L5" s="153" t="s">
         <v>92</v>
       </c>
@@ -7739,57 +7727,57 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
-      <c r="B6" s="331" t="s">
+      <c r="B6" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C6" s="284"/>
       <c r="D6" s="284"/>
-      <c r="E6" s="366">
+      <c r="E6" s="375">
         <v>52.034300000000002</v>
       </c>
       <c r="F6" s="284"/>
       <c r="G6" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="385" t="s">
+      <c r="H6" s="360" t="s">
         <v>300</v>
       </c>
-      <c r="I6" s="253"/>
+      <c r="I6" s="263"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1">
       <c r="B7" s="165"/>
-      <c r="C7" s="325" t="s">
+      <c r="C7" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D7" s="284"/>
-      <c r="E7" s="372" t="s">
+      <c r="E7" s="363" t="s">
         <v>136</v>
       </c>
       <c r="F7" s="284"/>
       <c r="G7" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="344">
+      <c r="H7" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I7" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I7" s="263"/>
     </row>
     <row r="8" spans="2:14" ht="15" customHeight="1">
       <c r="B8" s="165"/>
-      <c r="C8" s="325" t="s">
+      <c r="C8" s="346" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="284"/>
-      <c r="E8" s="363">
+      <c r="E8" s="373">
         <v>11173</v>
       </c>
       <c r="F8" s="284"/>
       <c r="G8" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="355"/>
-      <c r="I8" s="253"/>
+      <c r="H8" s="348"/>
+      <c r="I8" s="263"/>
       <c r="J8" s="226"/>
       <c r="K8" s="226"/>
       <c r="L8" s="226"/>
@@ -7797,7 +7785,7 @@
       <c r="N8" s="226"/>
     </row>
     <row r="9" spans="2:14" ht="15" customHeight="1">
-      <c r="B9" s="342" t="s">
+      <c r="B9" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="284"/>
@@ -7806,7 +7794,7 @@
       <c r="F9" s="284"/>
       <c r="G9" s="284"/>
       <c r="H9" s="284"/>
-      <c r="I9" s="253"/>
+      <c r="I9" s="263"/>
       <c r="J9" s="226"/>
       <c r="K9" s="226"/>
       <c r="L9" s="226"/>
@@ -7814,7 +7802,7 @@
       <c r="N9" s="226"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1">
-      <c r="B10" s="324" t="s">
+      <c r="B10" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="284"/>
@@ -7837,11 +7825,11 @@
       <c r="N10" s="226"/>
     </row>
     <row r="11" spans="2:14" ht="15" customHeight="1">
-      <c r="B11" s="351" t="s">
+      <c r="B11" s="383" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="352"/>
-      <c r="D11" s="352"/>
+      <c r="C11" s="384"/>
+      <c r="D11" s="384"/>
       <c r="E11" s="240">
         <v>7.23</v>
       </c>
@@ -7849,10 +7837,10 @@
         <f>E11/E6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="G11" s="353">
+      <c r="G11" s="385">
         <v>1</v>
       </c>
-      <c r="H11" s="353"/>
+      <c r="H11" s="385"/>
       <c r="I11" s="167"/>
       <c r="J11" s="226"/>
       <c r="K11" s="226"/>
@@ -7861,7 +7849,7 @@
       <c r="N11" s="226"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1">
-      <c r="B12" s="362" t="s">
+      <c r="B12" s="372" t="s">
         <v>117</v>
       </c>
       <c r="C12" s="284"/>
@@ -7874,7 +7862,7 @@
         <f>E12/E6</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="G12" s="327">
+      <c r="G12" s="326">
         <v>0.8</v>
       </c>
       <c r="H12" s="284"/>
@@ -7886,7 +7874,7 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="373" t="s">
+      <c r="B13" s="364" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="284"/>
@@ -7899,7 +7887,7 @@
         <f>E13/E6</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="G13" s="327">
+      <c r="G13" s="326">
         <v>0.6</v>
       </c>
       <c r="H13" s="284"/>
@@ -7915,11 +7903,11 @@
       <c r="N13" s="226"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1">
-      <c r="B14" s="354" t="s">
+      <c r="B14" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="259"/>
-      <c r="D14" s="259"/>
+      <c r="C14" s="251"/>
+      <c r="D14" s="251"/>
       <c r="E14" s="170">
         <f>SUM(E11:E13)</f>
         <v>52.034300000000002</v>
@@ -7928,11 +7916,11 @@
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="350">
+      <c r="G14" s="322">
         <f>(F12*G12)+(F13*G13)+F11*G11</f>
         <v>0.75109687263977798</v>
       </c>
-      <c r="H14" s="259"/>
+      <c r="H14" s="251"/>
       <c r="I14" s="172"/>
       <c r="J14" s="227"/>
       <c r="K14" s="228"/>
@@ -7956,7 +7944,7 @@
       <c r="N15" s="226"/>
     </row>
     <row r="16" spans="2:14" ht="15" customHeight="1">
-      <c r="B16" s="348" t="s">
+      <c r="B16" s="340" t="s">
         <v>108</v>
       </c>
       <c r="C16" s="284"/>
@@ -7969,52 +7957,52 @@
       <c r="K16" s="203"/>
     </row>
     <row r="17" spans="2:11" ht="15" customHeight="1">
-      <c r="B17" s="328" t="s">
+      <c r="B17" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="329"/>
-      <c r="D17" s="329"/>
-      <c r="E17" s="326" t="s">
+      <c r="C17" s="333"/>
+      <c r="D17" s="333"/>
+      <c r="E17" s="324" t="s">
         <v>110</v>
       </c>
       <c r="F17" s="284"/>
       <c r="G17" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="338" t="s">
+      <c r="H17" s="356" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="253"/>
+      <c r="I17" s="263"/>
       <c r="K17" s="203" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1">
-      <c r="B18" s="331" t="s">
+      <c r="B18" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C18" s="284"/>
       <c r="D18" s="284"/>
-      <c r="E18" s="323" t="s">
+      <c r="E18" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F18" s="284"/>
       <c r="G18" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="336" t="s">
+      <c r="H18" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="253"/>
+      <c r="I18" s="263"/>
       <c r="K18" s="203"/>
     </row>
     <row r="19" spans="2:11" ht="15" customHeight="1">
-      <c r="B19" s="331" t="s">
+      <c r="B19" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C19" s="284"/>
       <c r="D19" s="284"/>
-      <c r="E19" s="365">
+      <c r="E19" s="368">
         <f>3500*4.84</f>
         <v>16940</v>
       </c>
@@ -8022,18 +8010,18 @@
       <c r="G19" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="357" t="s">
+      <c r="H19" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="253"/>
+      <c r="I19" s="263"/>
     </row>
     <row r="20" spans="2:11" ht="15" customHeight="1">
       <c r="B20" s="211"/>
-      <c r="C20" s="325" t="s">
+      <c r="C20" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D20" s="284"/>
-      <c r="E20" s="371">
+      <c r="E20" s="352">
         <f>180000000</f>
         <v>180000000</v>
       </c>
@@ -8041,11 +8029,11 @@
       <c r="G20" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="360">
+      <c r="H20" s="328">
         <f>E20/E19</f>
         <v>10625.737898465171</v>
       </c>
-      <c r="I20" s="253"/>
+      <c r="I20" s="263"/>
       <c r="K20" s="221">
         <f>H20*4.84</f>
         <v>51428.571428571428</v>
@@ -8053,42 +8041,42 @@
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1">
       <c r="B21" s="212"/>
-      <c r="C21" s="325" t="s">
+      <c r="C21" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D21" s="284"/>
-      <c r="E21" s="332" t="s">
+      <c r="E21" s="370" t="s">
         <v>116</v>
       </c>
       <c r="F21" s="284"/>
       <c r="G21" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="344">
+      <c r="H21" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I21" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I21" s="263"/>
     </row>
     <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="212"/>
-      <c r="C22" s="325" t="s">
+      <c r="C22" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D22" s="284"/>
-      <c r="E22" s="326" t="s">
+      <c r="E22" s="324" t="s">
         <v>97</v>
       </c>
       <c r="F22" s="284"/>
       <c r="G22" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="368"/>
-      <c r="I22" s="253"/>
+      <c r="H22" s="365"/>
+      <c r="I22" s="263"/>
       <c r="K22" s="238"/>
     </row>
     <row r="23" spans="2:11" ht="15" customHeight="1">
-      <c r="B23" s="342" t="s">
+      <c r="B23" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C23" s="284"/>
@@ -8097,10 +8085,10 @@
       <c r="F23" s="284"/>
       <c r="G23" s="284"/>
       <c r="H23" s="284"/>
-      <c r="I23" s="253"/>
+      <c r="I23" s="263"/>
     </row>
     <row r="24" spans="2:11" ht="15" customHeight="1">
-      <c r="B24" s="324" t="s">
+      <c r="B24" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C24" s="284"/>
@@ -8118,7 +8106,7 @@
       <c r="I24" s="213"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1">
-      <c r="B25" s="335" t="s">
+      <c r="B25" s="334" t="s">
         <v>106</v>
       </c>
       <c r="C25" s="284"/>
@@ -8131,7 +8119,7 @@
         <f>E25/E19</f>
         <v>0.17142857142857143</v>
       </c>
-      <c r="G25" s="341">
+      <c r="G25" s="335">
         <v>1</v>
       </c>
       <c r="H25" s="284"/>
@@ -8151,14 +8139,14 @@
         <f>E26/E19</f>
         <v>0.47857142857142859</v>
       </c>
-      <c r="G26" s="341">
+      <c r="G26" s="335">
         <v>0.8</v>
       </c>
       <c r="H26" s="284"/>
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="374" t="s">
+      <c r="B27" s="361" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="284"/>
@@ -8171,18 +8159,18 @@
         <f>E27/E19</f>
         <v>0.35</v>
       </c>
-      <c r="G27" s="341">
+      <c r="G27" s="335">
         <v>0.6</v>
       </c>
       <c r="H27" s="284"/>
       <c r="I27" s="213"/>
     </row>
     <row r="28" spans="2:11" ht="15" customHeight="1">
-      <c r="B28" s="354" t="s">
+      <c r="B28" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="259"/>
-      <c r="D28" s="259"/>
+      <c r="C28" s="251"/>
+      <c r="D28" s="251"/>
       <c r="E28" s="170">
         <f>SUM(E25:E27)</f>
         <v>16940</v>
@@ -8191,11 +8179,11 @@
         <f>SUM(F25:F27)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="350">
+      <c r="G28" s="322">
         <f>F25*G25+F26*G26+F27*G27</f>
         <v>0.76428571428571423</v>
       </c>
-      <c r="H28" s="259"/>
+      <c r="H28" s="251"/>
       <c r="I28" s="216"/>
     </row>
     <row r="29" spans="2:11" ht="15" customHeight="1">
@@ -8209,7 +8197,7 @@
       <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:11" ht="15" customHeight="1">
-      <c r="B30" s="348" t="s">
+      <c r="B30" s="340" t="s">
         <v>118</v>
       </c>
       <c r="C30" s="284"/>
@@ -8221,83 +8209,83 @@
       <c r="I30" s="284"/>
     </row>
     <row r="31" spans="2:11" ht="15" customHeight="1">
-      <c r="B31" s="328" t="s">
+      <c r="B31" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="329"/>
-      <c r="D31" s="329"/>
-      <c r="E31" s="326" t="s">
+      <c r="C31" s="333"/>
+      <c r="D31" s="333"/>
+      <c r="E31" s="324" t="s">
         <v>119</v>
       </c>
       <c r="F31" s="284"/>
       <c r="G31" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="338" t="s">
+      <c r="H31" s="356" t="s">
         <v>120</v>
       </c>
-      <c r="I31" s="253"/>
+      <c r="I31" s="263"/>
       <c r="J31" s="185"/>
       <c r="K31" s="152" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15" customHeight="1">
-      <c r="B32" s="331" t="s">
+      <c r="B32" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C32" s="284"/>
       <c r="D32" s="284"/>
-      <c r="E32" s="323" t="s">
+      <c r="E32" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F32" s="284"/>
       <c r="G32" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="336" t="s">
+      <c r="H32" s="359" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="253"/>
+      <c r="I32" s="263"/>
       <c r="K32" s="203"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1">
-      <c r="B33" s="331" t="s">
+      <c r="B33" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="284"/>
       <c r="D33" s="284"/>
-      <c r="E33" s="377">
+      <c r="E33" s="357">
         <v>1258.4000000000001</v>
       </c>
       <c r="F33" s="284"/>
       <c r="G33" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="336" t="s">
+      <c r="H33" s="359" t="s">
         <v>95</v>
       </c>
-      <c r="I33" s="253"/>
+      <c r="I33" s="263"/>
       <c r="K33" s="203"/>
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="211"/>
-      <c r="C34" s="325" t="s">
+      <c r="C34" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="284"/>
-      <c r="E34" s="371">
+      <c r="E34" s="352">
         <v>16900000</v>
       </c>
       <c r="F34" s="284"/>
       <c r="G34" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="360">
+      <c r="H34" s="328">
         <f>E34/E33</f>
         <v>13429.752066115701</v>
       </c>
-      <c r="I34" s="253"/>
+      <c r="I34" s="263"/>
       <c r="K34" s="221">
         <f>H34*4.84</f>
         <v>64999.999999999993</v>
@@ -8305,41 +8293,41 @@
     </row>
     <row r="35" spans="2:11" ht="15" customHeight="1">
       <c r="B35" s="212"/>
-      <c r="C35" s="325" t="s">
+      <c r="C35" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D35" s="284"/>
-      <c r="E35" s="332" t="s">
+      <c r="E35" s="370" t="s">
         <v>116</v>
       </c>
       <c r="F35" s="284"/>
       <c r="G35" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H35" s="344">
+      <c r="H35" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I35" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I35" s="263"/>
     </row>
     <row r="36" spans="2:11" ht="15" customHeight="1">
       <c r="B36" s="212"/>
-      <c r="C36" s="325" t="s">
+      <c r="C36" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D36" s="284"/>
-      <c r="E36" s="326" t="s">
+      <c r="E36" s="324" t="s">
         <v>97</v>
       </c>
       <c r="F36" s="284"/>
       <c r="G36" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="368"/>
-      <c r="I36" s="253"/>
+      <c r="H36" s="365"/>
+      <c r="I36" s="263"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1">
-      <c r="B37" s="342" t="s">
+      <c r="B37" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C37" s="284"/>
@@ -8348,11 +8336,11 @@
       <c r="F37" s="284"/>
       <c r="G37" s="284"/>
       <c r="H37" s="284"/>
-      <c r="I37" s="253"/>
+      <c r="I37" s="263"/>
       <c r="K37" s="238"/>
     </row>
     <row r="38" spans="2:11" ht="15" customHeight="1">
-      <c r="B38" s="324" t="s">
+      <c r="B38" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C38" s="284"/>
@@ -8370,7 +8358,7 @@
       <c r="I38" s="213"/>
     </row>
     <row r="39" spans="2:11" ht="15" customHeight="1">
-      <c r="B39" s="335" t="s">
+      <c r="B39" s="334" t="s">
         <v>106</v>
       </c>
       <c r="C39" s="284"/>
@@ -8382,7 +8370,7 @@
         <f>E39/E33</f>
         <v>0.11538461538461536</v>
       </c>
-      <c r="G39" s="341">
+      <c r="G39" s="335">
         <v>1</v>
       </c>
       <c r="H39" s="284"/>
@@ -8402,14 +8390,14 @@
         <f>E40/E33</f>
         <v>0.53341538461538451</v>
       </c>
-      <c r="G40" s="341">
+      <c r="G40" s="335">
         <v>0.8</v>
       </c>
       <c r="H40" s="284"/>
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="374" t="s">
+      <c r="B41" s="361" t="s">
         <v>107</v>
       </c>
       <c r="C41" s="284"/>
@@ -8422,18 +8410,18 @@
         <f>E41/E33</f>
         <v>0.35120000000000001</v>
       </c>
-      <c r="G41" s="341">
+      <c r="G41" s="335">
         <v>0.6</v>
       </c>
       <c r="H41" s="284"/>
       <c r="I41" s="213"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1">
-      <c r="B42" s="354" t="s">
+      <c r="B42" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="259"/>
-      <c r="D42" s="259"/>
+      <c r="C42" s="251"/>
+      <c r="D42" s="251"/>
       <c r="E42" s="170">
         <f>SUM(E39:E41)</f>
         <v>1258.4000000000001</v>
@@ -8442,11 +8430,11 @@
         <f>F39+F41+F40</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G42" s="350">
+      <c r="G42" s="322">
         <f>F41*G41+F39*G39+F40*G40</f>
         <v>0.75283692307692296</v>
       </c>
-      <c r="H42" s="259"/>
+      <c r="H42" s="251"/>
       <c r="I42" s="216"/>
     </row>
     <row r="43" spans="2:11" ht="15" customHeight="1">
@@ -8460,7 +8448,7 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="384" t="s">
+      <c r="B44" s="358" t="s">
         <v>122</v>
       </c>
       <c r="C44" s="284"/>
@@ -8472,81 +8460,81 @@
       <c r="I44" s="284"/>
     </row>
     <row r="45" spans="2:11" ht="15" customHeight="1">
-      <c r="B45" s="328" t="s">
+      <c r="B45" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="329"/>
-      <c r="D45" s="329"/>
-      <c r="E45" s="323" t="s">
+      <c r="C45" s="333"/>
+      <c r="D45" s="333"/>
+      <c r="E45" s="347" t="s">
         <v>119</v>
       </c>
       <c r="F45" s="284"/>
       <c r="G45" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H45" s="338" t="s">
+      <c r="H45" s="356" t="s">
         <v>120</v>
       </c>
-      <c r="I45" s="253"/>
+      <c r="I45" s="263"/>
       <c r="K45" s="203" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1">
-      <c r="B46" s="331" t="s">
+      <c r="B46" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="284"/>
       <c r="D46" s="284"/>
-      <c r="E46" s="323" t="s">
+      <c r="E46" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F46" s="284"/>
       <c r="G46" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H46" s="336" t="s">
+      <c r="H46" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I46" s="253"/>
+      <c r="I46" s="263"/>
     </row>
     <row r="47" spans="2:11" ht="15" customHeight="1">
-      <c r="B47" s="331" t="s">
+      <c r="B47" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C47" s="284"/>
       <c r="D47" s="284"/>
-      <c r="E47" s="365">
+      <c r="E47" s="368">
         <v>430.76</v>
       </c>
       <c r="F47" s="284"/>
       <c r="G47" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H47" s="357" t="s">
+      <c r="H47" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="I47" s="253"/>
+      <c r="I47" s="263"/>
       <c r="K47" s="203"/>
     </row>
     <row r="48" spans="2:11" ht="15" customHeight="1">
       <c r="B48" s="164"/>
-      <c r="C48" s="325" t="s">
+      <c r="C48" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D48" s="284"/>
-      <c r="E48" s="347">
+      <c r="E48" s="323">
         <v>7120000</v>
       </c>
       <c r="F48" s="284"/>
       <c r="G48" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H48" s="361">
+      <c r="H48" s="343">
         <f>E48/E47</f>
         <v>16528.92561983471</v>
       </c>
-      <c r="I48" s="253"/>
+      <c r="I48" s="263"/>
       <c r="J48" s="221"/>
       <c r="K48" s="221">
         <f>H48*4.84</f>
@@ -8555,42 +8543,42 @@
     </row>
     <row r="49" spans="2:11" ht="15" customHeight="1">
       <c r="B49" s="165"/>
-      <c r="C49" s="325" t="s">
+      <c r="C49" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D49" s="284"/>
-      <c r="E49" s="332" t="s">
+      <c r="E49" s="370" t="s">
         <v>116</v>
       </c>
       <c r="F49" s="284"/>
       <c r="G49" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H49" s="344">
+      <c r="H49" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I49" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I49" s="263"/>
     </row>
     <row r="50" spans="2:11" ht="15" customHeight="1">
       <c r="B50" s="165"/>
-      <c r="C50" s="325" t="s">
+      <c r="C50" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D50" s="284"/>
-      <c r="E50" s="326" t="s">
+      <c r="E50" s="324" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="284"/>
       <c r="G50" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H50" s="355"/>
-      <c r="I50" s="253"/>
+      <c r="H50" s="348"/>
+      <c r="I50" s="263"/>
       <c r="K50" s="238"/>
     </row>
     <row r="51" spans="2:11" ht="15" customHeight="1">
-      <c r="B51" s="342" t="s">
+      <c r="B51" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C51" s="284"/>
@@ -8599,10 +8587,10 @@
       <c r="F51" s="284"/>
       <c r="G51" s="284"/>
       <c r="H51" s="284"/>
-      <c r="I51" s="253"/>
+      <c r="I51" s="263"/>
     </row>
     <row r="52" spans="2:11" ht="15" customHeight="1">
-      <c r="B52" s="324" t="s">
+      <c r="B52" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C52" s="284"/>
@@ -8620,7 +8608,7 @@
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="2:11" ht="15" customHeight="1">
-      <c r="B53" s="335" t="s">
+      <c r="B53" s="334" t="s">
         <v>106</v>
       </c>
       <c r="C53" s="284"/>
@@ -8632,7 +8620,7 @@
         <f>E53/E47</f>
         <v>0.33707865168539325</v>
       </c>
-      <c r="G53" s="327">
+      <c r="G53" s="326">
         <v>1</v>
       </c>
       <c r="H53" s="284"/>
@@ -8652,7 +8640,7 @@
         <f>E54/E47</f>
         <v>0.31042134831460677</v>
       </c>
-      <c r="G54" s="327">
+      <c r="G54" s="326">
         <v>0.8</v>
       </c>
       <c r="H54" s="284"/>
@@ -8672,18 +8660,18 @@
         <f>E55/E47</f>
         <v>0.35249999999999998</v>
       </c>
-      <c r="G55" s="327">
+      <c r="G55" s="326">
         <v>0.6</v>
       </c>
       <c r="H55" s="284"/>
       <c r="I55" s="167"/>
     </row>
     <row r="56" spans="2:11" ht="15" customHeight="1">
-      <c r="B56" s="354" t="s">
+      <c r="B56" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="259"/>
-      <c r="D56" s="259"/>
+      <c r="C56" s="251"/>
+      <c r="D56" s="251"/>
       <c r="E56" s="170">
         <f>SUM(E53:E55)</f>
         <v>430.76</v>
@@ -8692,11 +8680,11 @@
         <f>SUM(F53:F55)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="350">
+      <c r="G56" s="322">
         <f>F53*G53+F55*G55+F54*G54</f>
         <v>0.79691573033707863</v>
       </c>
-      <c r="H56" s="259"/>
+      <c r="H56" s="251"/>
       <c r="I56" s="172"/>
     </row>
     <row r="57" spans="2:11" ht="15" customHeight="1">
@@ -8710,7 +8698,7 @@
       <c r="I57" s="173"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="340" t="s">
         <v>125</v>
       </c>
       <c r="C58" s="284"/>
@@ -8723,80 +8711,80 @@
       <c r="K58" s="203"/>
     </row>
     <row r="59" spans="2:11" ht="15" customHeight="1">
-      <c r="B59" s="328" t="s">
+      <c r="B59" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="329"/>
-      <c r="D59" s="329"/>
-      <c r="E59" s="323" t="s">
+      <c r="C59" s="333"/>
+      <c r="D59" s="333"/>
+      <c r="E59" s="347" t="s">
         <v>126</v>
       </c>
       <c r="F59" s="284"/>
       <c r="G59" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H59" s="367" t="s">
+      <c r="H59" s="369" t="s">
         <v>127</v>
       </c>
-      <c r="I59" s="253"/>
+      <c r="I59" s="263"/>
       <c r="K59" s="203" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" customHeight="1">
-      <c r="B60" s="331" t="s">
+      <c r="B60" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C60" s="284"/>
       <c r="D60" s="284"/>
-      <c r="E60" s="323" t="s">
+      <c r="E60" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F60" s="284"/>
       <c r="G60" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H60" s="336" t="s">
+      <c r="H60" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I60" s="253"/>
+      <c r="I60" s="263"/>
     </row>
     <row r="61" spans="2:11" ht="15" customHeight="1">
-      <c r="B61" s="331" t="s">
+      <c r="B61" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C61" s="284"/>
       <c r="D61" s="284"/>
-      <c r="E61" s="369">
+      <c r="E61" s="338">
         <v>626</v>
       </c>
       <c r="F61" s="284"/>
       <c r="G61" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H61" s="336" t="s">
+      <c r="H61" s="359" t="s">
         <v>129</v>
       </c>
-      <c r="I61" s="253"/>
+      <c r="I61" s="263"/>
     </row>
     <row r="62" spans="2:11" ht="15" customHeight="1">
       <c r="B62" s="164"/>
-      <c r="C62" s="325" t="s">
+      <c r="C62" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D62" s="284"/>
-      <c r="E62" s="378">
+      <c r="E62" s="362">
         <v>10500000</v>
       </c>
       <c r="F62" s="284"/>
       <c r="G62" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H62" s="330">
+      <c r="H62" s="339">
         <f>E62/E61</f>
         <v>16773.162939297126</v>
       </c>
-      <c r="I62" s="253"/>
+      <c r="I62" s="263"/>
       <c r="J62" s="221"/>
       <c r="K62" s="221">
         <f>H62*4.84</f>
@@ -8805,42 +8793,42 @@
     </row>
     <row r="63" spans="2:11" ht="15" customHeight="1">
       <c r="B63" s="165"/>
-      <c r="C63" s="325" t="s">
+      <c r="C63" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D63" s="284"/>
-      <c r="E63" s="375" t="s">
+      <c r="E63" s="366" t="s">
         <v>116</v>
       </c>
       <c r="F63" s="284"/>
       <c r="G63" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="344">
+      <c r="H63" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I63" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I63" s="263"/>
     </row>
     <row r="64" spans="2:11" ht="15" customHeight="1">
       <c r="B64" s="165"/>
-      <c r="C64" s="325" t="s">
+      <c r="C64" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D64" s="284"/>
-      <c r="E64" s="326" t="s">
+      <c r="E64" s="324" t="s">
         <v>97</v>
       </c>
       <c r="F64" s="284"/>
       <c r="G64" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H64" s="355"/>
-      <c r="I64" s="253"/>
+      <c r="H64" s="348"/>
+      <c r="I64" s="263"/>
       <c r="K64" s="238"/>
     </row>
     <row r="65" spans="2:11" ht="15" customHeight="1">
-      <c r="B65" s="342" t="s">
+      <c r="B65" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C65" s="284"/>
@@ -8849,10 +8837,10 @@
       <c r="F65" s="284"/>
       <c r="G65" s="284"/>
       <c r="H65" s="284"/>
-      <c r="I65" s="253"/>
+      <c r="I65" s="263"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
-      <c r="B66" s="324" t="s">
+      <c r="B66" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C66" s="284"/>
@@ -8882,7 +8870,7 @@
         <f>E67/E61</f>
         <v>0.30830670926517573</v>
       </c>
-      <c r="G67" s="327">
+      <c r="G67" s="326">
         <v>1</v>
       </c>
       <c r="H67" s="284"/>
@@ -8901,14 +8889,14 @@
         <f>E68/E61</f>
         <v>0.27156549520766771</v>
       </c>
-      <c r="G68" s="327">
+      <c r="G68" s="326">
         <v>0.9</v>
       </c>
       <c r="H68" s="284"/>
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="376" t="s">
+      <c r="B69" s="367" t="s">
         <v>107</v>
       </c>
       <c r="C69" s="284"/>
@@ -8921,18 +8909,18 @@
         <f>E69/E61</f>
         <v>0.42012779552715657</v>
       </c>
-      <c r="G69" s="327">
+      <c r="G69" s="326">
         <v>0.6</v>
       </c>
       <c r="H69" s="284"/>
       <c r="I69" s="167"/>
     </row>
     <row r="70" spans="2:11" ht="15" customHeight="1">
-      <c r="B70" s="354" t="s">
+      <c r="B70" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="259"/>
-      <c r="D70" s="259"/>
+      <c r="C70" s="251"/>
+      <c r="D70" s="251"/>
       <c r="E70" s="170">
         <f>SUM(E67:E69)</f>
         <v>626</v>
@@ -8941,11 +8929,11 @@
         <f>SUM(F67:F69)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="350">
+      <c r="G70" s="322">
         <f>F67*G67+F69*G69+F68*G68</f>
         <v>0.80479233226837055</v>
       </c>
-      <c r="H70" s="259"/>
+      <c r="H70" s="251"/>
       <c r="I70" s="172"/>
     </row>
     <row r="71" spans="2:11" ht="15" customHeight="1">
@@ -8959,7 +8947,7 @@
       <c r="I71" s="173"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1">
-      <c r="B72" s="348" t="s">
+      <c r="B72" s="340" t="s">
         <v>131</v>
       </c>
       <c r="C72" s="284"/>
@@ -8971,51 +8959,51 @@
       <c r="I72" s="284"/>
     </row>
     <row r="73" spans="2:11" ht="15" customHeight="1">
-      <c r="B73" s="328" t="s">
+      <c r="B73" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C73" s="329"/>
-      <c r="D73" s="329"/>
-      <c r="E73" s="326" t="s">
+      <c r="C73" s="333"/>
+      <c r="D73" s="333"/>
+      <c r="E73" s="324" t="s">
         <v>132</v>
       </c>
       <c r="F73" s="284"/>
       <c r="G73" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H73" s="338" t="s">
+      <c r="H73" s="356" t="s">
         <v>133</v>
       </c>
-      <c r="I73" s="253"/>
+      <c r="I73" s="263"/>
       <c r="K73" s="203" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" customHeight="1">
-      <c r="B74" s="331" t="s">
+      <c r="B74" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C74" s="284"/>
       <c r="D74" s="284"/>
-      <c r="E74" s="326" t="s">
+      <c r="E74" s="324" t="s">
         <v>135</v>
       </c>
       <c r="F74" s="284"/>
       <c r="G74" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H74" s="336" t="s">
+      <c r="H74" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I74" s="253"/>
+      <c r="I74" s="263"/>
     </row>
     <row r="75" spans="2:11" ht="15" customHeight="1">
-      <c r="B75" s="331" t="s">
+      <c r="B75" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C75" s="284"/>
       <c r="D75" s="284"/>
-      <c r="E75" s="388">
+      <c r="E75" s="341">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
@@ -9023,48 +9011,48 @@
       <c r="G75" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H75" s="357" t="s">
+      <c r="H75" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="I75" s="253"/>
+      <c r="I75" s="263"/>
     </row>
     <row r="76" spans="2:11" ht="15" customHeight="1">
       <c r="B76" s="164"/>
-      <c r="C76" s="325" t="s">
+      <c r="C76" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D76" s="284"/>
-      <c r="E76" s="347">
+      <c r="E76" s="323">
         <v>60000000</v>
       </c>
       <c r="F76" s="284"/>
       <c r="G76" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H76" s="361">
+      <c r="H76" s="343">
         <f>E76/E75</f>
         <v>16981.772897090457</v>
       </c>
-      <c r="I76" s="253"/>
+      <c r="I76" s="263"/>
     </row>
     <row r="77" spans="2:11" ht="15" customHeight="1">
       <c r="B77" s="165"/>
-      <c r="C77" s="325" t="s">
+      <c r="C77" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D77" s="284"/>
-      <c r="E77" s="359" t="s">
+      <c r="E77" s="379" t="s">
         <v>116</v>
       </c>
       <c r="F77" s="284"/>
       <c r="G77" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H77" s="344">
+      <c r="H77" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I77" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I77" s="263"/>
       <c r="K77" s="221">
         <f>H76*4.84</f>
         <v>82191.780821917811</v>
@@ -9072,22 +9060,22 @@
     </row>
     <row r="78" spans="2:11" ht="15" customHeight="1">
       <c r="B78" s="165"/>
-      <c r="C78" s="325" t="s">
+      <c r="C78" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D78" s="284"/>
-      <c r="E78" s="326" t="s">
+      <c r="E78" s="324" t="s">
         <v>136</v>
       </c>
       <c r="F78" s="284"/>
       <c r="G78" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H78" s="355"/>
-      <c r="I78" s="253"/>
+      <c r="H78" s="348"/>
+      <c r="I78" s="263"/>
     </row>
     <row r="79" spans="2:11" ht="15" customHeight="1">
-      <c r="B79" s="342" t="s">
+      <c r="B79" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C79" s="284"/>
@@ -9096,11 +9084,11 @@
       <c r="F79" s="284"/>
       <c r="G79" s="284"/>
       <c r="H79" s="284"/>
-      <c r="I79" s="253"/>
+      <c r="I79" s="263"/>
       <c r="K79" s="238"/>
     </row>
     <row r="80" spans="2:11" ht="15" customHeight="1">
-      <c r="B80" s="324" t="s">
+      <c r="B80" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C80" s="284"/>
@@ -9118,7 +9106,7 @@
       <c r="I80" s="167"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="334" t="s">
+      <c r="B81" s="344" t="s">
         <v>130</v>
       </c>
       <c r="C81" s="284"/>
@@ -9131,14 +9119,14 @@
         <f>E81/E75</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="G81" s="327">
+      <c r="G81" s="326">
         <v>0.9</v>
       </c>
       <c r="H81" s="284"/>
       <c r="I81" s="167"/>
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1">
-      <c r="B82" s="334" t="s">
+      <c r="B82" s="344" t="s">
         <v>117</v>
       </c>
       <c r="C82" s="284"/>
@@ -9151,7 +9139,7 @@
         <f>E82/E75</f>
         <v>8.6756164383561624E-2</v>
       </c>
-      <c r="G82" s="327">
+      <c r="G82" s="326">
         <v>0.8</v>
       </c>
       <c r="H82" s="284"/>
@@ -9171,18 +9159,18 @@
         <f>E83/E75</f>
         <v>0.35160000000000002</v>
       </c>
-      <c r="G83" s="327">
+      <c r="G83" s="326">
         <v>0.6</v>
       </c>
       <c r="H83" s="284"/>
       <c r="I83" s="167"/>
     </row>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="354" t="s">
+      <c r="B84" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="259"/>
-      <c r="D84" s="259"/>
+      <c r="C84" s="251"/>
+      <c r="D84" s="251"/>
       <c r="E84" s="170">
         <f>SUM(E81:E83)</f>
         <v>3533.2</v>
@@ -9191,11 +9179,11 @@
         <f>SUM(F81:F83)</f>
         <v>1</v>
       </c>
-      <c r="G84" s="350">
+      <c r="G84" s="322">
         <f>F81*G81+F83*G83+F82*G82</f>
         <v>0.78584438356164399</v>
       </c>
-      <c r="H84" s="259"/>
+      <c r="H84" s="251"/>
       <c r="I84" s="172"/>
     </row>
     <row r="85" spans="2:11" ht="15" customHeight="1">
@@ -9209,7 +9197,7 @@
       <c r="I85" s="173"/>
     </row>
     <row r="86" spans="2:11" ht="15" customHeight="1">
-      <c r="B86" s="348" t="s">
+      <c r="B86" s="340" t="s">
         <v>137</v>
       </c>
       <c r="C86" s="284"/>
@@ -9222,52 +9210,52 @@
       <c r="K86" s="203"/>
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1">
-      <c r="B87" s="328" t="s">
+      <c r="B87" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="329"/>
-      <c r="D87" s="329"/>
-      <c r="E87" s="323" t="s">
+      <c r="C87" s="333"/>
+      <c r="D87" s="333"/>
+      <c r="E87" s="347" t="s">
         <v>119</v>
       </c>
       <c r="F87" s="284"/>
       <c r="G87" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H87" s="370" t="str">
+      <c r="H87" s="371" t="str">
         <f>H45</f>
         <v>(63) 99252-2282</v>
       </c>
-      <c r="I87" s="253"/>
+      <c r="I87" s="263"/>
       <c r="K87" s="203" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1">
-      <c r="B88" s="331" t="s">
+      <c r="B88" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C88" s="284"/>
       <c r="D88" s="284"/>
-      <c r="E88" s="323" t="s">
+      <c r="E88" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F88" s="284"/>
       <c r="G88" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H88" s="336" t="s">
+      <c r="H88" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I88" s="253"/>
+      <c r="I88" s="263"/>
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1">
-      <c r="B89" s="331" t="s">
+      <c r="B89" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C89" s="284"/>
       <c r="D89" s="284"/>
-      <c r="E89" s="377">
+      <c r="E89" s="357">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
@@ -9275,29 +9263,29 @@
       <c r="G89" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H89" s="357" t="s">
+      <c r="H89" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="I89" s="253"/>
+      <c r="I89" s="263"/>
     </row>
     <row r="90" spans="2:11" ht="15" customHeight="1">
       <c r="B90" s="164"/>
-      <c r="C90" s="325" t="s">
+      <c r="C90" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D90" s="284"/>
-      <c r="E90" s="358">
+      <c r="E90" s="349">
         <v>43980000</v>
       </c>
       <c r="F90" s="284"/>
       <c r="G90" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H90" s="330">
+      <c r="H90" s="339">
         <f>E90/E89</f>
         <v>12396.694214876034</v>
       </c>
-      <c r="I90" s="253"/>
+      <c r="I90" s="263"/>
       <c r="K90" s="221">
         <f>H90*4.84</f>
         <v>60000</v>
@@ -9305,41 +9293,41 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1">
       <c r="B91" s="165"/>
-      <c r="C91" s="325" t="s">
+      <c r="C91" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D91" s="284"/>
-      <c r="E91" s="333" t="s">
+      <c r="E91" s="377" t="s">
         <v>116</v>
       </c>
       <c r="F91" s="284"/>
       <c r="G91" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H91" s="344">
+      <c r="H91" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I91" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I91" s="263"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1">
       <c r="B92" s="165"/>
-      <c r="C92" s="325" t="s">
+      <c r="C92" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D92" s="284"/>
-      <c r="E92" s="326" t="s">
+      <c r="E92" s="324" t="s">
         <v>97</v>
       </c>
       <c r="F92" s="284"/>
       <c r="G92" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H92" s="355"/>
-      <c r="I92" s="253"/>
+      <c r="H92" s="348"/>
+      <c r="I92" s="263"/>
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1">
-      <c r="B93" s="342" t="s">
+      <c r="B93" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C93" s="284"/>
@@ -9348,10 +9336,10 @@
       <c r="F93" s="284"/>
       <c r="G93" s="284"/>
       <c r="H93" s="284"/>
-      <c r="I93" s="253"/>
+      <c r="I93" s="263"/>
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1">
-      <c r="B94" s="324" t="s">
+      <c r="B94" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C94" s="284"/>
@@ -9369,7 +9357,7 @@
       <c r="I94" s="167"/>
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1">
-      <c r="B95" s="335" t="s">
+      <c r="B95" s="334" t="s">
         <v>106</v>
       </c>
       <c r="C95" s="284"/>
@@ -9381,7 +9369,7 @@
         <f>E95/E89</f>
         <v>0.31005829095870024</v>
       </c>
-      <c r="G95" s="345">
+      <c r="G95" s="381">
         <v>1</v>
       </c>
       <c r="H95" s="284"/>
@@ -9401,14 +9389,14 @@
         <f>E96/E89</f>
         <v>0.33854170904129977</v>
       </c>
-      <c r="G96" s="345">
+      <c r="G96" s="381">
         <v>0.8</v>
       </c>
       <c r="H96" s="284"/>
       <c r="I96" s="206"/>
     </row>
     <row r="97" spans="2:12" ht="15" customHeight="1">
-      <c r="B97" s="346" t="s">
+      <c r="B97" s="378" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="284"/>
@@ -9421,7 +9409,7 @@
         <f>E97/E89</f>
         <v>0.35139999999999999</v>
       </c>
-      <c r="G97" s="327">
+      <c r="G97" s="326">
         <v>0.6</v>
       </c>
       <c r="H97" s="284"/>
@@ -9430,11 +9418,11 @@
       <c r="L97" s="207"/>
     </row>
     <row r="98" spans="2:12" ht="15" customHeight="1">
-      <c r="B98" s="354" t="s">
+      <c r="B98" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C98" s="259"/>
-      <c r="D98" s="259"/>
+      <c r="C98" s="251"/>
+      <c r="D98" s="251"/>
       <c r="E98" s="170">
         <f>SUM(E95:E97)</f>
         <v>3547.72</v>
@@ -9443,11 +9431,11 @@
         <f>SUM(F95:F97)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="350">
+      <c r="G98" s="322">
         <f>F97*G97+F95*G95+F96*G96</f>
         <v>0.79173165819173996</v>
       </c>
-      <c r="H98" s="259"/>
+      <c r="H98" s="251"/>
       <c r="I98" s="172"/>
       <c r="K98" s="207"/>
       <c r="L98" s="207"/>
@@ -9468,7 +9456,7 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="386"/>
+      <c r="B100" s="342"/>
       <c r="C100" s="284"/>
       <c r="D100" s="284"/>
       <c r="E100" s="284"/>
@@ -9480,7 +9468,7 @@
       <c r="L100" s="207"/>
     </row>
     <row r="101" spans="2:12" ht="15" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="340" t="s">
         <v>139</v>
       </c>
       <c r="C101" s="284"/>
@@ -9494,93 +9482,93 @@
       <c r="L101" s="207"/>
     </row>
     <row r="102" spans="2:12" ht="15" customHeight="1">
-      <c r="B102" s="328" t="s">
+      <c r="B102" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C102" s="329"/>
-      <c r="D102" s="329"/>
-      <c r="E102" s="339"/>
+      <c r="C102" s="333"/>
+      <c r="D102" s="333"/>
+      <c r="E102" s="387"/>
       <c r="F102" s="284"/>
       <c r="G102" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H102" s="387"/>
-      <c r="I102" s="253"/>
+      <c r="H102" s="325"/>
+      <c r="I102" s="263"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
     </row>
     <row r="103" spans="2:12" ht="15" customHeight="1">
-      <c r="B103" s="331" t="s">
+      <c r="B103" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C103" s="284"/>
       <c r="D103" s="284"/>
-      <c r="E103" s="349"/>
+      <c r="E103" s="382"/>
       <c r="F103" s="284"/>
       <c r="G103" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H103" s="356"/>
-      <c r="I103" s="253"/>
+      <c r="H103" s="376"/>
+      <c r="I103" s="263"/>
     </row>
     <row r="104" spans="2:12" ht="15" customHeight="1">
-      <c r="B104" s="331" t="s">
+      <c r="B104" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C104" s="284"/>
       <c r="D104" s="284"/>
-      <c r="E104" s="369"/>
+      <c r="E104" s="338"/>
       <c r="F104" s="284"/>
       <c r="G104" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H104" s="380"/>
-      <c r="I104" s="253"/>
+      <c r="H104" s="351"/>
+      <c r="I104" s="263"/>
     </row>
     <row r="105" spans="2:12" ht="15" customHeight="1">
       <c r="B105" s="164"/>
-      <c r="C105" s="325" t="s">
+      <c r="C105" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D105" s="284"/>
-      <c r="E105" s="358"/>
+      <c r="E105" s="349"/>
       <c r="F105" s="284"/>
       <c r="G105" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H105" s="330"/>
-      <c r="I105" s="253"/>
+      <c r="H105" s="339"/>
+      <c r="I105" s="263"/>
     </row>
     <row r="106" spans="2:12" ht="15" customHeight="1">
       <c r="B106" s="165"/>
-      <c r="C106" s="325" t="s">
+      <c r="C106" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D106" s="284"/>
-      <c r="E106" s="333"/>
+      <c r="E106" s="377"/>
       <c r="F106" s="284"/>
       <c r="G106" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H106" s="343"/>
-      <c r="I106" s="253"/>
+      <c r="H106" s="380"/>
+      <c r="I106" s="263"/>
     </row>
     <row r="107" spans="2:12" ht="15" customHeight="1">
       <c r="B107" s="165"/>
-      <c r="C107" s="325" t="s">
+      <c r="C107" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D107" s="284"/>
-      <c r="E107" s="379"/>
+      <c r="E107" s="350"/>
       <c r="F107" s="284"/>
       <c r="G107" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H107" s="355"/>
-      <c r="I107" s="253"/>
+      <c r="H107" s="348"/>
+      <c r="I107" s="263"/>
     </row>
     <row r="108" spans="2:12" ht="15" customHeight="1">
-      <c r="B108" s="342" t="s">
+      <c r="B108" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C108" s="284"/>
@@ -9589,10 +9577,10 @@
       <c r="F108" s="284"/>
       <c r="G108" s="284"/>
       <c r="H108" s="284"/>
-      <c r="I108" s="253"/>
+      <c r="I108" s="263"/>
     </row>
     <row r="109" spans="2:12" ht="15" customHeight="1">
-      <c r="B109" s="324" t="s">
+      <c r="B109" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C109" s="284"/>
@@ -9610,35 +9598,35 @@
       <c r="I109" s="167"/>
     </row>
     <row r="110" spans="2:12" ht="15" customHeight="1">
-      <c r="B110" s="346" t="s">
+      <c r="B110" s="378" t="s">
         <v>106</v>
       </c>
       <c r="C110" s="284"/>
       <c r="D110" s="284"/>
       <c r="E110" s="168"/>
       <c r="F110" s="169"/>
-      <c r="G110" s="327"/>
+      <c r="G110" s="326"/>
       <c r="H110" s="284"/>
       <c r="I110" s="167"/>
     </row>
     <row r="111" spans="2:12" ht="15" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="378" t="s">
         <v>107</v>
       </c>
       <c r="C111" s="284"/>
       <c r="D111" s="284"/>
       <c r="E111" s="168"/>
       <c r="F111" s="169"/>
-      <c r="G111" s="327"/>
+      <c r="G111" s="326"/>
       <c r="H111" s="284"/>
       <c r="I111" s="167"/>
     </row>
     <row r="112" spans="2:12" ht="15" customHeight="1">
-      <c r="B112" s="354" t="s">
+      <c r="B112" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C112" s="259"/>
-      <c r="D112" s="259"/>
+      <c r="C112" s="251"/>
+      <c r="D112" s="251"/>
       <c r="E112" s="170">
         <f>SUM(E110:E111)</f>
         <v>0</v>
@@ -9647,15 +9635,220 @@
         <f>SUM(F110:F111)</f>
         <v>0</v>
       </c>
-      <c r="G112" s="350">
+      <c r="G112" s="322">
         <f>F110*G110+F111*G111</f>
         <v>0</v>
       </c>
-      <c r="H112" s="259"/>
+      <c r="H112" s="251"/>
       <c r="I112" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="229">
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B75:D75"/>
     <mergeCell ref="G112:H112"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E22:F22"/>
@@ -9680,211 +9873,6 @@
     <mergeCell ref="E75:F75"/>
     <mergeCell ref="H89:I89"/>
     <mergeCell ref="G84:H84"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B100:I100"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="G39:H39"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9892,7 +9880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B3:M10"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -10207,7 +10195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10236,7 +10224,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="396"/>
+      <c r="E1" s="390"/>
       <c r="F1" s="391"/>
       <c r="G1" s="391"/>
       <c r="H1" s="391"/>
@@ -10796,8 +10784,8 @@
       <c r="A12" s="389" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="251"/>
-      <c r="C12" s="397" t="s">
+      <c r="B12" s="249"/>
+      <c r="C12" s="392" t="s">
         <v>174</v>
       </c>
       <c r="D12" s="391"/>
@@ -10825,8 +10813,8 @@
       <c r="A13" s="389" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="251"/>
-      <c r="C13" s="397" t="s">
+      <c r="B13" s="249"/>
+      <c r="C13" s="392" t="s">
         <v>177</v>
       </c>
       <c r="D13" s="391"/>
@@ -10855,8 +10843,8 @@
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
-      <c r="B14" s="251"/>
-      <c r="C14" s="397" t="s">
+      <c r="B14" s="249"/>
+      <c r="C14" s="392" t="s">
         <v>179</v>
       </c>
       <c r="D14" s="391"/>
@@ -10884,8 +10872,8 @@
       <c r="A15" s="389" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="251"/>
-      <c r="C15" s="397" t="s">
+      <c r="B15" s="249"/>
+      <c r="C15" s="392" t="s">
         <v>181</v>
       </c>
       <c r="D15" s="391"/>
@@ -10913,8 +10901,8 @@
       <c r="A16" s="389" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="251"/>
-      <c r="C16" s="390" t="s">
+      <c r="B16" s="249"/>
+      <c r="C16" s="394" t="s">
         <v>183</v>
       </c>
       <c r="D16" s="391"/>
@@ -10937,8 +10925,8 @@
       <c r="A17" s="389" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="251"/>
-      <c r="C17" s="390" t="s">
+      <c r="B17" s="249"/>
+      <c r="C17" s="394" t="s">
         <v>184</v>
       </c>
       <c r="D17" s="391"/>
@@ -10970,8 +10958,8 @@
       <c r="A18" s="389" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="251"/>
-      <c r="C18" s="390" t="s">
+      <c r="B18" s="249"/>
+      <c r="C18" s="394" t="s">
         <v>187</v>
       </c>
       <c r="D18" s="391"/>
@@ -10998,8 +10986,8 @@
       <c r="A19" s="389" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="251"/>
-      <c r="C19" s="390" t="s">
+      <c r="B19" s="249"/>
+      <c r="C19" s="394" t="s">
         <v>189</v>
       </c>
       <c r="D19" s="391"/>
@@ -11027,8 +11015,8 @@
       <c r="A20" s="389" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="251"/>
-      <c r="C20" s="390" t="s">
+      <c r="B20" s="249"/>
+      <c r="C20" s="394" t="s">
         <v>191</v>
       </c>
       <c r="D20" s="391"/>
@@ -11056,8 +11044,8 @@
       <c r="A21" s="389" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="251"/>
-      <c r="C21" s="390" t="s">
+      <c r="B21" s="249"/>
+      <c r="C21" s="394" t="s">
         <v>193</v>
       </c>
       <c r="D21" s="391"/>
@@ -11085,8 +11073,8 @@
       <c r="A22" s="389" t="s">
         <v>192</v>
       </c>
-      <c r="B22" s="251"/>
-      <c r="C22" s="398" t="s">
+      <c r="B22" s="249"/>
+      <c r="C22" s="393" t="s">
         <v>195</v>
       </c>
       <c r="D22" s="391"/>
@@ -11100,7 +11088,7 @@
       <c r="L22" s="391"/>
       <c r="M22" s="391"/>
       <c r="N22" s="391"/>
-      <c r="O22" s="253"/>
+      <c r="O22" s="263"/>
       <c r="P22" s="147" t="s">
         <v>196</v>
       </c>
@@ -11114,8 +11102,8 @@
       <c r="A23" s="389" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="251"/>
-      <c r="C23" s="390" t="s">
+      <c r="B23" s="249"/>
+      <c r="C23" s="394" t="s">
         <v>197</v>
       </c>
       <c r="D23" s="391"/>
@@ -11143,8 +11131,8 @@
       <c r="A24" s="389" t="s">
         <v>196</v>
       </c>
-      <c r="B24" s="251"/>
-      <c r="C24" s="390" t="s">
+      <c r="B24" s="249"/>
+      <c r="C24" s="394" t="s">
         <v>199</v>
       </c>
       <c r="D24" s="391"/>
@@ -11172,8 +11160,8 @@
       <c r="A25" s="389" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="251"/>
-      <c r="C25" s="390" t="s">
+      <c r="B25" s="249"/>
+      <c r="C25" s="394" t="s">
         <v>201</v>
       </c>
       <c r="D25" s="391"/>
@@ -11193,21 +11181,21 @@
       <c r="R25" s="146"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="392" t="s">
+      <c r="A26" s="395" t="s">
         <v>202</v>
       </c>
-      <c r="B26" s="393"/>
-      <c r="C26" s="394" t="s">
+      <c r="B26" s="396"/>
+      <c r="C26" s="397" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="395"/>
-      <c r="E26" s="395"/>
-      <c r="F26" s="395"/>
-      <c r="G26" s="395"/>
-      <c r="H26" s="395"/>
-      <c r="I26" s="395"/>
-      <c r="J26" s="395"/>
-      <c r="K26" s="395"/>
+      <c r="D26" s="398"/>
+      <c r="E26" s="398"/>
+      <c r="F26" s="398"/>
+      <c r="G26" s="398"/>
+      <c r="H26" s="398"/>
+      <c r="I26" s="398"/>
+      <c r="J26" s="398"/>
+      <c r="K26" s="398"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
@@ -11228,21 +11216,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C23:L23"/>
@@ -11259,6 +11232,21 @@
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:K17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C10">
     <cfRule type="cellIs" dxfId="8" priority="25" stopIfTrue="1" operator="equal">
@@ -11306,7 +11294,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="C4:L34"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -11315,367 +11303,386 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="415" t="str">
-        <f>'AREA UTIL '!C4</f>
+      <c r="C4" s="399" t="str">
+        <f>'AREA UTIL'!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="415" t="s">
+      <c r="C5" s="399" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="400" t="s">
+      <c r="C6" s="404" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
+      <c r="D6" s="253"/>
+      <c r="E6" s="253"/>
       <c r="F6" s="401">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
-      <c r="G6" s="248"/>
-      <c r="H6" s="253"/>
+      <c r="G6" s="253"/>
+      <c r="H6" s="263"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="400" t="s">
+      <c r="C7" s="404" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253"/>
       <c r="F7" s="401">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
-      <c r="G7" s="248"/>
-      <c r="H7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="263"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="400" t="s">
+      <c r="C8" s="404" t="s">
         <v>206</v>
       </c>
-      <c r="D8" s="248"/>
-      <c r="E8" s="248"/>
+      <c r="D8" s="253"/>
+      <c r="E8" s="253"/>
       <c r="F8" s="401">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="253"/>
+      <c r="G8" s="253"/>
+      <c r="H8" s="263"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="400" t="s">
+      <c r="C9" s="404" t="s">
         <v>207</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="403">
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="400">
         <v>6</v>
       </c>
-      <c r="G9" s="248"/>
-      <c r="H9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="263"/>
       <c r="J9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="400" t="s">
+      <c r="C10" s="404" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="248"/>
-      <c r="E10" s="248"/>
-      <c r="F10" s="403">
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="400">
         <v>1</v>
       </c>
-      <c r="G10" s="248"/>
-      <c r="H10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="263"/>
       <c r="J10" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="400" t="s">
+      <c r="C11" s="404" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="412">
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="415">
         <f>'PLANILHA HOMOG'!Q24</f>
         <v>1.9255773964901695</v>
       </c>
-      <c r="G11" s="248"/>
-      <c r="H11" s="253"/>
+      <c r="G11" s="253"/>
+      <c r="H11" s="263"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="400" t="s">
+      <c r="C12" s="404" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="403">
+      <c r="D12" s="253"/>
+      <c r="E12" s="253"/>
+      <c r="F12" s="400">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
-      <c r="G12" s="248"/>
-      <c r="H12" s="253"/>
+      <c r="G12" s="253"/>
+      <c r="H12" s="263"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="400" t="s">
+      <c r="C13" s="404" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
       <c r="F13" s="401">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
-      <c r="G13" s="248"/>
-      <c r="H13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="263"/>
     </row>
     <row r="14" spans="3:12" ht="15" customHeight="1">
-      <c r="C14" s="410" t="s">
+      <c r="C14" s="412" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="250"/>
-      <c r="E14" s="250"/>
-      <c r="F14" s="409">
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="408">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G14" s="250"/>
-      <c r="H14" s="251"/>
-      <c r="J14" s="413">
+      <c r="G14" s="248"/>
+      <c r="H14" s="249"/>
+      <c r="J14" s="406">
         <f>F14*4.84</f>
         <v>63838.680399999997</v>
       </c>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
+      <c r="K14" s="253"/>
+      <c r="L14" s="253"/>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="417"/>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="248"/>
-      <c r="G15" s="248"/>
-      <c r="H15" s="248"/>
+      <c r="C15" s="410"/>
+      <c r="D15" s="253"/>
+      <c r="E15" s="253"/>
+      <c r="F15" s="253"/>
+      <c r="G15" s="253"/>
+      <c r="H15" s="253"/>
     </row>
     <row r="16" spans="3:12">
-      <c r="C16" s="399" t="s">
+      <c r="C16" s="414" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="248"/>
-      <c r="H16" s="248"/>
+      <c r="D16" s="253"/>
+      <c r="E16" s="253"/>
+      <c r="F16" s="253"/>
+      <c r="G16" s="253"/>
+      <c r="H16" s="253"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="400" t="s">
+      <c r="C17" s="404" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="403">
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="400">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G17" s="248"/>
-      <c r="H17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="263"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="400" t="s">
+      <c r="C18" s="404" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
+      <c r="D18" s="253"/>
+      <c r="E18" s="253"/>
       <c r="F18" s="401">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G18" s="248"/>
-      <c r="H18" s="253"/>
+      <c r="G18" s="253"/>
+      <c r="H18" s="263"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="400" t="s">
+      <c r="C19" s="404" t="s">
         <v>215</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="E19" s="248"/>
+      <c r="D19" s="253"/>
+      <c r="E19" s="253"/>
       <c r="F19" s="401">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G19" s="248"/>
-      <c r="H19" s="253"/>
+      <c r="G19" s="253"/>
+      <c r="H19" s="263"/>
     </row>
     <row r="20" spans="3:8" ht="15" customHeight="1">
-      <c r="C20" s="410" t="s">
+      <c r="C20" s="412" t="s">
         <v>216</v>
       </c>
-      <c r="D20" s="250"/>
-      <c r="E20" s="250"/>
-      <c r="F20" s="409">
+      <c r="D20" s="248"/>
+      <c r="E20" s="248"/>
+      <c r="F20" s="408">
         <f>F19</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G20" s="250"/>
-      <c r="H20" s="251"/>
+      <c r="G20" s="248"/>
+      <c r="H20" s="249"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="404"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="407"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
+      <c r="C21" s="405"/>
+      <c r="D21" s="253"/>
+      <c r="E21" s="253"/>
+      <c r="F21" s="402"/>
+      <c r="G21" s="253"/>
+      <c r="H21" s="253"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="404"/>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="407"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
+      <c r="C22" s="405"/>
+      <c r="D22" s="253"/>
+      <c r="E22" s="253"/>
+      <c r="F22" s="402"/>
+      <c r="G22" s="253"/>
+      <c r="H22" s="253"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="404"/>
-      <c r="D23" s="248"/>
-      <c r="E23" s="248"/>
-      <c r="F23" s="416"/>
-      <c r="G23" s="248"/>
-      <c r="H23" s="248"/>
+      <c r="C23" s="405"/>
+      <c r="D23" s="253"/>
+      <c r="E23" s="253"/>
+      <c r="F23" s="409"/>
+      <c r="G23" s="253"/>
+      <c r="H23" s="253"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="414" t="s">
+      <c r="C24" s="407" t="s">
         <v>217</v>
       </c>
-      <c r="D24" s="248"/>
-      <c r="E24" s="248"/>
-      <c r="F24" s="248"/>
-      <c r="G24" s="248"/>
-      <c r="H24" s="248"/>
+      <c r="D24" s="253"/>
+      <c r="E24" s="253"/>
+      <c r="F24" s="253"/>
+      <c r="G24" s="253"/>
+      <c r="H24" s="253"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="405" t="s">
+      <c r="C25" s="403" t="s">
         <v>218</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
-      <c r="F25" s="408">
+      <c r="D25" s="253"/>
+      <c r="E25" s="253"/>
+      <c r="F25" s="411">
         <v>2000000</v>
       </c>
-      <c r="G25" s="248"/>
-      <c r="H25" s="253"/>
+      <c r="G25" s="253"/>
+      <c r="H25" s="263"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="405" t="s">
+      <c r="C26" s="403" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="402">
+      <c r="D26" s="253"/>
+      <c r="E26" s="253"/>
+      <c r="F26" s="416">
         <v>0.8</v>
       </c>
-      <c r="G26" s="248"/>
-      <c r="H26" s="253"/>
+      <c r="G26" s="253"/>
+      <c r="H26" s="263"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="405" t="s">
+      <c r="C27" s="403" t="s">
         <v>220</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="E27" s="248"/>
-      <c r="F27" s="408">
+      <c r="D27" s="253"/>
+      <c r="E27" s="253"/>
+      <c r="F27" s="411">
         <f>F25*F26</f>
         <v>1600000</v>
       </c>
-      <c r="G27" s="248"/>
-      <c r="H27" s="253"/>
+      <c r="G27" s="253"/>
+      <c r="H27" s="263"/>
     </row>
     <row r="28" spans="3:8" ht="15" customHeight="1">
-      <c r="C28" s="411" t="s">
+      <c r="C28" s="413" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="250"/>
-      <c r="E28" s="250"/>
-      <c r="F28" s="406">
+      <c r="D28" s="248"/>
+      <c r="E28" s="248"/>
+      <c r="F28" s="417">
         <f>F27</f>
         <v>1600000</v>
       </c>
-      <c r="G28" s="250"/>
-      <c r="H28" s="251"/>
+      <c r="G28" s="248"/>
+      <c r="H28" s="249"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="399" t="s">
+      <c r="C31" s="414" t="s">
         <v>221</v>
       </c>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
+      <c r="D31" s="253"/>
+      <c r="E31" s="253"/>
+      <c r="F31" s="253"/>
+      <c r="G31" s="253"/>
+      <c r="H31" s="253"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="400" t="s">
+      <c r="C32" s="404" t="s">
         <v>222</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="E32" s="248"/>
+      <c r="D32" s="253"/>
+      <c r="E32" s="253"/>
       <c r="F32" s="401">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G32" s="248"/>
-      <c r="H32" s="253"/>
+      <c r="G32" s="253"/>
+      <c r="H32" s="263"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="400" t="s">
+      <c r="C33" s="404" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="401">
         <f>F28</f>
         <v>1600000</v>
       </c>
-      <c r="G33" s="248"/>
-      <c r="H33" s="253"/>
+      <c r="G33" s="253"/>
+      <c r="H33" s="263"/>
     </row>
     <row r="34" spans="3:8" ht="15" customHeight="1">
-      <c r="C34" s="410" t="s">
+      <c r="C34" s="412" t="s">
         <v>224</v>
       </c>
-      <c r="D34" s="250"/>
-      <c r="E34" s="250"/>
-      <c r="F34" s="409">
+      <c r="D34" s="248"/>
+      <c r="E34" s="248"/>
+      <c r="F34" s="408">
         <f>F32+F33</f>
         <v>2286322.530483</v>
       </c>
-      <c r="G34" s="250"/>
-      <c r="H34" s="251"/>
+      <c r="G34" s="248"/>
+      <c r="H34" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="F19:H19"/>
@@ -11692,34 +11699,15 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C15:H15"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C22:E22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -11727,7 +11715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="C5:K18"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -11737,169 +11725,178 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="415" t="str">
+      <c r="C5" s="399" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="415" t="s">
+      <c r="C6" s="399" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
-      <c r="F6" s="248"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="248"/>
+      <c r="D6" s="253"/>
+      <c r="E6" s="253"/>
+      <c r="F6" s="253"/>
+      <c r="G6" s="253"/>
+      <c r="H6" s="253"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="400" t="s">
+      <c r="C7" s="404" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253"/>
       <c r="F7" s="419">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G7" s="248"/>
-      <c r="H7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="263"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="400" t="s">
+      <c r="C8" s="404" t="s">
         <v>227</v>
       </c>
-      <c r="D8" s="248"/>
-      <c r="E8" s="248"/>
-      <c r="F8" s="403">
+      <c r="D8" s="253"/>
+      <c r="E8" s="253"/>
+      <c r="F8" s="400">
         <v>36</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="253"/>
+      <c r="G8" s="253"/>
+      <c r="H8" s="263"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="400" t="s">
+      <c r="C9" s="404" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
       <c r="F9" s="418">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
-      <c r="G9" s="248"/>
-      <c r="H9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="263"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="400" t="s">
+      <c r="C10" s="404" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="248"/>
-      <c r="E10" s="248"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
       <c r="F10" s="401">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G10" s="248"/>
-      <c r="H10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="263"/>
     </row>
     <row r="11" spans="3:11" ht="15" customHeight="1">
-      <c r="C11" s="410" t="s">
+      <c r="C11" s="412" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="250"/>
-      <c r="E11" s="250"/>
-      <c r="F11" s="409">
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="408">
         <f>F10/((1+F7)^(F8/12))</f>
         <v>472512.85039331613</v>
       </c>
-      <c r="G11" s="250"/>
-      <c r="H11" s="251"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="249"/>
       <c r="K11" s="188"/>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1">
       <c r="K12" s="188"/>
     </row>
     <row r="13" spans="3:11">
-      <c r="C13" s="399" t="s">
+      <c r="C13" s="414" t="s">
         <v>225</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="253"/>
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="400" t="s">
+      <c r="C14" s="404" t="s">
         <v>226</v>
       </c>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
+      <c r="D14" s="253"/>
+      <c r="E14" s="253"/>
       <c r="F14" s="419">
         <v>0.12767999999999999</v>
       </c>
-      <c r="G14" s="248"/>
-      <c r="H14" s="253"/>
+      <c r="G14" s="253"/>
+      <c r="H14" s="263"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="400" t="s">
+      <c r="C15" s="404" t="s">
         <v>227</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="403">
+      <c r="D15" s="253"/>
+      <c r="E15" s="253"/>
+      <c r="F15" s="400">
         <v>36</v>
       </c>
-      <c r="G15" s="248"/>
-      <c r="H15" s="253"/>
+      <c r="G15" s="253"/>
+      <c r="H15" s="263"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="400" t="s">
+      <c r="C16" s="404" t="s">
         <v>228</v>
       </c>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
+      <c r="D16" s="253"/>
+      <c r="E16" s="253"/>
       <c r="F16" s="418">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
-      <c r="G16" s="248"/>
-      <c r="H16" s="253"/>
+      <c r="G16" s="253"/>
+      <c r="H16" s="263"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="400" t="s">
+      <c r="C17" s="404" t="s">
         <v>229</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
       <c r="F17" s="401">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
-      <c r="G17" s="248"/>
-      <c r="H17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="263"/>
     </row>
     <row r="18" spans="3:8" ht="15" customHeight="1">
-      <c r="C18" s="410" t="s">
+      <c r="C18" s="412" t="s">
         <v>230</v>
       </c>
-      <c r="D18" s="250"/>
-      <c r="E18" s="250"/>
-      <c r="F18" s="409">
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="408">
         <f>F17/((1+F14)^(F15/12))</f>
         <v>1115738.3182275943</v>
       </c>
-      <c r="G18" s="250"/>
-      <c r="H18" s="251"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C17:E17"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="C14:E14"/>
@@ -11914,15 +11911,6 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C17:E17"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
